--- a/research/traditional_assets/database/data/taiwan/taiwan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_bank_money_center.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05</v>
+        <v>0.0398</v>
       </c>
       <c r="E2">
-        <v>0.0617</v>
+        <v>0.0312</v>
       </c>
       <c r="F2">
-        <v>0.121</v>
+        <v>-0.00315</v>
       </c>
       <c r="G2">
-        <v>0.1140060656189688</v>
+        <v>0.141702860352751</v>
       </c>
       <c r="H2">
-        <v>0.1140060656189688</v>
+        <v>0.141702860352751</v>
       </c>
       <c r="I2">
-        <v>0.1103722579364894</v>
+        <v>-0.0006777381611011258</v>
       </c>
       <c r="J2">
-        <v>0.09496042432225706</v>
+        <v>-0.0005562187959479574</v>
       </c>
       <c r="K2">
-        <v>8781.299999999999</v>
+        <v>6634.7</v>
       </c>
       <c r="L2">
-        <v>0.2631621534146078</v>
+        <v>0.2700666343738933</v>
       </c>
       <c r="M2">
-        <v>3848.3305</v>
+        <v>4123.2059</v>
       </c>
       <c r="N2">
-        <v>0.03133439427952146</v>
+        <v>0.03772071324541117</v>
       </c>
       <c r="O2">
-        <v>0.4382415473790897</v>
+        <v>0.6214607894855834</v>
       </c>
       <c r="P2">
-        <v>3848.3305</v>
+        <v>4111.8799</v>
       </c>
       <c r="Q2">
-        <v>0.03133439427952146</v>
+        <v>0.03761709853186569</v>
       </c>
       <c r="R2">
-        <v>0.4382415473790897</v>
+        <v>0.6197537040107315</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>11.326</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.002746891684453595</v>
       </c>
       <c r="U2">
-        <v>40125.1</v>
+        <v>40647.7</v>
       </c>
       <c r="V2">
-        <v>0.3267119869006122</v>
+        <v>0.3718611859246465</v>
       </c>
       <c r="W2">
-        <v>0.09446930741315415</v>
+        <v>0.07171917092748363</v>
       </c>
       <c r="X2">
-        <v>0.06918615418698497</v>
+        <v>0.09568346776625192</v>
       </c>
       <c r="Y2">
-        <v>0.02528315322616918</v>
+        <v>-0.02396429683876829</v>
       </c>
       <c r="Z2">
-        <v>0.1839914657368499</v>
+        <v>0.1287045540697215</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04537658713606496</v>
+        <v>0.07215887094608762</v>
       </c>
       <c r="AC2">
-        <v>-0.04435462149040321</v>
+        <v>-0.07130346153022768</v>
       </c>
       <c r="AD2">
-        <v>136621.6</v>
+        <v>129940.7</v>
       </c>
       <c r="AE2">
-        <v>126.271741360233</v>
+        <v>128.7496281497762</v>
       </c>
       <c r="AF2">
-        <v>136747.8717413602</v>
+        <v>130069.4496281498</v>
       </c>
       <c r="AG2">
-        <v>96622.77174136022</v>
+        <v>89421.74962814979</v>
       </c>
       <c r="AH2">
-        <v>0.5268393106759617</v>
+        <v>0.5433636925251133</v>
       </c>
       <c r="AI2">
-        <v>0.5820939111421194</v>
+        <v>0.6186381762685859</v>
       </c>
       <c r="AJ2">
-        <v>0.4403198911773201</v>
+        <v>0.4499647879778388</v>
       </c>
       <c r="AK2">
-        <v>0.4960127400962304</v>
+        <v>0.5272398474218496</v>
       </c>
       <c r="AL2">
-        <v>529.4</v>
+        <v>703.7</v>
       </c>
       <c r="AM2">
-        <v>529.4</v>
+        <v>703.7</v>
       </c>
       <c r="AN2">
-        <v>35.86433559090671</v>
+        <v>1601.635646493282</v>
       </c>
       <c r="AO2">
-        <v>6.877786173026068</v>
+        <v>-0.08938468097200511</v>
       </c>
       <c r="AP2">
-        <v>25.36430192191952</v>
+        <v>1102.203249453344</v>
       </c>
       <c r="AQ2">
-        <v>6.877786173026068</v>
+        <v>-0.08938468097200511</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CTBC Financial Holding Co., Ltd. (TWSE:2891)</t>
+          <t>Union Bank of Taiwan (TWSE:2838)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,49 +725,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0186</v>
+        <v>0.049</v>
       </c>
       <c r="E3">
-        <v>0.0951</v>
-      </c>
-      <c r="F3">
-        <v>0.137</v>
+        <v>0.0433</v>
       </c>
       <c r="G3">
-        <v>0.2491355372766804</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.2491355372766804</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.238454183475664</v>
+        <v>0.09677772414740479</v>
       </c>
       <c r="J3">
-        <v>0.2080025720943355</v>
+        <v>0.07439425351750353</v>
       </c>
       <c r="K3">
-        <v>1911.1</v>
+        <v>102.7</v>
       </c>
       <c r="L3">
-        <v>0.1251571750406035</v>
+        <v>0.2148985143335426</v>
       </c>
       <c r="M3">
-        <v>735.4</v>
+        <v>30.6</v>
       </c>
       <c r="N3">
-        <v>0.04031599318016106</v>
+        <v>0.01634790041671119</v>
       </c>
       <c r="O3">
-        <v>0.3848045628172257</v>
+        <v>0.2979552093476144</v>
       </c>
       <c r="P3">
-        <v>735.4</v>
+        <v>30.6</v>
       </c>
       <c r="Q3">
-        <v>0.04031599318016106</v>
+        <v>0.01634790041671119</v>
       </c>
       <c r="R3">
-        <v>0.3848045628172257</v>
+        <v>0.2979552093476144</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +773,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14463.4</v>
+        <v>272</v>
       </c>
       <c r="V3">
-        <v>0.7929104375332356</v>
+        <v>0.1453146703707661</v>
       </c>
       <c r="W3">
-        <v>0.1506380697896222</v>
+        <v>0.04618844164605352</v>
       </c>
       <c r="X3">
-        <v>0.05504389348491455</v>
+        <v>0.105719982515143</v>
       </c>
       <c r="Y3">
-        <v>0.09559417630470764</v>
+        <v>-0.0595315408690895</v>
       </c>
       <c r="Z3">
-        <v>1.360817759716244</v>
+        <v>0.08905329093059398</v>
       </c>
       <c r="AA3">
-        <v>0.2830535941726302</v>
+        <v>0.006625053102058608</v>
       </c>
       <c r="AB3">
-        <v>0.04537658713606496</v>
+        <v>0.07432694948498544</v>
       </c>
       <c r="AC3">
-        <v>0.2376770070365652</v>
+        <v>-0.06770189638292684</v>
       </c>
       <c r="AD3">
-        <v>10717.4</v>
+        <v>2614.6</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>128.7496281497762</v>
       </c>
       <c r="AF3">
-        <v>10717.4</v>
+        <v>2743.349628149776</v>
       </c>
       <c r="AG3">
-        <v>-3746</v>
+        <v>2471.349628149776</v>
       </c>
       <c r="AH3">
-        <v>0.3700976921987824</v>
+        <v>0.5944226838100569</v>
       </c>
       <c r="AI3">
-        <v>0.4184212478380879</v>
+        <v>0.5894289836878285</v>
       </c>
       <c r="AJ3">
-        <v>-0.2584357256690284</v>
+        <v>0.569022446781921</v>
       </c>
       <c r="AK3">
-        <v>-0.335949060580243</v>
+        <v>0.563945424805296</v>
       </c>
       <c r="AL3">
-        <v>529.4</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>529.4</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>2.863853779761109</v>
-      </c>
-      <c r="AO3">
-        <v>6.877786173026068</v>
+        <v>36.31388888888889</v>
       </c>
       <c r="AP3">
-        <v>-1.000988696790744</v>
-      </c>
-      <c r="AQ3">
-        <v>6.877786173026068</v>
+        <v>34.32430039096911</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Union Bank of Taiwan (TWSE:2838)</t>
+          <t>O-Bank Co., Ltd. (TWSE:2897)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,10 +853,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.05139999999999999</v>
+        <v>0.0374</v>
       </c>
       <c r="E4">
-        <v>0.0941</v>
+        <v>0.106</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -874,100 +865,97 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.07440549738256293</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.06503000575526947</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>163</v>
+        <v>65.8</v>
       </c>
       <c r="L4">
-        <v>0.2898293029871977</v>
+        <v>0.2433431952662722</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>25.8</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.03458445040214477</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.39209726443769</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>25.8</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.03458445040214477</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.39209726443769</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>303.7</v>
+        <v>600.3</v>
       </c>
       <c r="V4">
-        <v>0.1879680633781023</v>
+        <v>0.8046916890080429</v>
       </c>
       <c r="W4">
-        <v>0.0846445448408371</v>
+        <v>0.05561189993238674</v>
       </c>
       <c r="X4">
-        <v>0.08860312836335327</v>
+        <v>0.3143380328515837</v>
       </c>
       <c r="Y4">
-        <v>-0.003958583522516171</v>
+        <v>-0.2587261329191969</v>
       </c>
       <c r="Z4">
-        <v>0.1073267748532791</v>
+        <v>0.02737590232148462</v>
       </c>
       <c r="AA4">
-        <v>0.006979460786403253</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04798168267032078</v>
+        <v>0.06846459864387146</v>
       </c>
       <c r="AC4">
-        <v>-0.04100222188391753</v>
+        <v>-0.06846459864387146</v>
       </c>
       <c r="AD4">
-        <v>3317.4</v>
+        <v>7408.8</v>
       </c>
       <c r="AE4">
-        <v>126.271741360233</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>3443.671741360233</v>
+        <v>7408.8</v>
       </c>
       <c r="AG4">
-        <v>3139.971741360233</v>
+        <v>6808.5</v>
       </c>
       <c r="AH4">
-        <v>0.6806520487926012</v>
+        <v>0.9085201353803894</v>
       </c>
       <c r="AI4">
-        <v>0.5980183451498172</v>
+        <v>0.8240698515099272</v>
       </c>
       <c r="AJ4">
-        <v>0.6602583004314188</v>
+        <v>0.9012509100536105</v>
       </c>
       <c r="AK4">
-        <v>0.5756376050626881</v>
+        <v>0.811482443803485</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>49.43964232488823</v>
-      </c>
-      <c r="AP4">
-        <v>46.7954059815236</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EnTie Commercial Bank Co., Ltd. (TWSE:2849)</t>
+          <t>Mega Financial Holding Co., Ltd. (TWSE:2886)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,10 +975,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.00232</v>
+        <v>-0.004</v>
       </c>
       <c r="E5">
-        <v>0.0617</v>
+        <v>-0.061</v>
+      </c>
+      <c r="F5">
+        <v>0.0235</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1005,28 +996,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>89.40000000000001</v>
+        <v>619.3</v>
       </c>
       <c r="L5">
-        <v>0.4320927984533591</v>
+        <v>0.3645085344320188</v>
       </c>
       <c r="M5">
-        <v>51.3</v>
+        <v>537.2</v>
       </c>
       <c r="N5">
-        <v>0.04445022095139069</v>
+        <v>0.03900809643103511</v>
       </c>
       <c r="O5">
-        <v>0.5738255033557046</v>
+        <v>0.8674309704505088</v>
       </c>
       <c r="P5">
-        <v>51.3</v>
+        <v>537.2</v>
       </c>
       <c r="Q5">
-        <v>0.04445022095139069</v>
+        <v>0.03900809643103511</v>
       </c>
       <c r="R5">
-        <v>0.5738255033557046</v>
+        <v>0.8674309704505088</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1035,55 +1026,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>169.3</v>
+        <v>2868.9</v>
       </c>
       <c r="V5">
-        <v>0.1466943939000087</v>
+        <v>0.2083215336020041</v>
       </c>
       <c r="W5">
-        <v>0.07643638850889194</v>
+        <v>0.0532997108234646</v>
       </c>
       <c r="X5">
-        <v>0.05033344033802079</v>
+        <v>0.1089285381353864</v>
       </c>
       <c r="Y5">
-        <v>0.02610294817087114</v>
+        <v>-0.05562882731192183</v>
       </c>
       <c r="Z5">
-        <v>0.1374056954627564</v>
+        <v>0.0607275872668654</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04288256081667018</v>
+        <v>0.06883276429938397</v>
       </c>
       <c r="AC5">
-        <v>-0.04288256081667018</v>
+        <v>-0.06883276429938397</v>
       </c>
       <c r="AD5">
-        <v>428</v>
+        <v>21976.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>428</v>
+        <v>21976.9</v>
       </c>
       <c r="AG5">
-        <v>258.7</v>
+        <v>19108</v>
       </c>
       <c r="AH5">
-        <v>0.2705265153909361</v>
+        <v>0.6147659755401641</v>
       </c>
       <c r="AI5">
-        <v>0.2564256185968486</v>
+        <v>0.7046836973216318</v>
       </c>
       <c r="AJ5">
-        <v>0.1831115515288788</v>
+        <v>0.5811523897869493</v>
       </c>
       <c r="AK5">
-        <v>0.1724896652887052</v>
+        <v>0.6747651670315701</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1100,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Taichung Commercial Bank Co., Ltd. (TWSE:2812)</t>
+          <t>Far Eastern International Bank Ltd. (TWSE:2845)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,10 +1100,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0602</v>
+        <v>0.00607</v>
       </c>
       <c r="E6">
-        <v>0.07820000000000001</v>
+        <v>-0.00157</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1127,28 +1118,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>167.2</v>
+        <v>101.5</v>
       </c>
       <c r="L6">
-        <v>0.3787089467723669</v>
+        <v>0.3094512195121951</v>
       </c>
       <c r="M6">
-        <v>35.8</v>
+        <v>35.4</v>
       </c>
       <c r="N6">
-        <v>0.01883714811891607</v>
+        <v>0.02429483220094709</v>
       </c>
       <c r="O6">
-        <v>0.2141148325358852</v>
+        <v>0.3487684729064039</v>
       </c>
       <c r="P6">
-        <v>35.8</v>
+        <v>35.4</v>
       </c>
       <c r="Q6">
-        <v>0.01883714811891607</v>
+        <v>0.02429483220094709</v>
       </c>
       <c r="R6">
-        <v>0.2141148325358852</v>
+        <v>0.3487684729064039</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1157,55 +1148,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>549.9</v>
+        <v>874.8</v>
       </c>
       <c r="V6">
-        <v>0.289344909234412</v>
+        <v>0.6003705991352687</v>
       </c>
       <c r="W6">
-        <v>0.09026128266033254</v>
+        <v>0.05725406137184116</v>
       </c>
       <c r="X6">
-        <v>0.05548499908724046</v>
+        <v>0.1073239835436853</v>
       </c>
       <c r="Y6">
-        <v>0.03477628357309208</v>
+        <v>-0.05006992217184415</v>
       </c>
       <c r="Z6">
-        <v>0.1721650288566527</v>
+        <v>0.144207518135854</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04312522478494216</v>
+        <v>0.06884518680129105</v>
       </c>
       <c r="AC6">
-        <v>-0.04312522478494216</v>
+        <v>-0.06884518680129105</v>
       </c>
       <c r="AD6">
-        <v>1155.2</v>
+        <v>2230.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1155.2</v>
+        <v>2230.4</v>
       </c>
       <c r="AG6">
-        <v>605.3000000000001</v>
+        <v>1355.6</v>
       </c>
       <c r="AH6">
-        <v>0.3780475832051576</v>
+        <v>0.6048542372881356</v>
       </c>
       <c r="AI6">
-        <v>0.3482245131729668</v>
+        <v>0.5752011553538271</v>
       </c>
       <c r="AJ6">
-        <v>0.2415595817702929</v>
+        <v>0.481956838624809</v>
       </c>
       <c r="AK6">
-        <v>0.2187172538392051</v>
+        <v>0.4514453177034768</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1231,10 +1222,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.09269999999999999</v>
+        <v>-0.176</v>
       </c>
       <c r="E7">
-        <v>0.12</v>
+        <v>-0.317</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1249,85 +1240,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>277.3</v>
+        <v>25.7</v>
       </c>
       <c r="L7">
-        <v>0.7123041356280504</v>
+        <v>0.2542037586547972</v>
       </c>
       <c r="M7">
-        <v>72.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="N7">
-        <v>0.04422889214250854</v>
+        <v>0.06940140270755178</v>
       </c>
       <c r="O7">
-        <v>0.2614496934727731</v>
+        <v>3.311284046692607</v>
       </c>
       <c r="P7">
-        <v>72.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Q7">
-        <v>0.04422889214250854</v>
+        <v>0.06043059859729244</v>
       </c>
       <c r="R7">
-        <v>0.2614496934727731</v>
+        <v>2.883268482490272</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.1292596944770858</v>
       </c>
       <c r="U7">
-        <v>182.3</v>
+        <v>92.5</v>
       </c>
       <c r="V7">
-        <v>0.1112127867252318</v>
+        <v>0.07543630729081716</v>
       </c>
       <c r="W7">
-        <v>0.1876310981798498</v>
+        <v>0.01450829852094388</v>
       </c>
       <c r="X7">
-        <v>0.05948227635495892</v>
+        <v>0.1036129486796114</v>
       </c>
       <c r="Y7">
-        <v>0.1281488218248908</v>
+        <v>-0.08910465015866753</v>
       </c>
       <c r="Z7">
-        <v>0.1229277842685276</v>
+        <v>0.03502026395095085</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04326928677192499</v>
+        <v>0.06887652157663122</v>
       </c>
       <c r="AC7">
-        <v>-0.04326928677192499</v>
+        <v>-0.06887652157663122</v>
       </c>
       <c r="AD7">
-        <v>1297.8</v>
+        <v>1692.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1297.8</v>
+        <v>1692.3</v>
       </c>
       <c r="AG7">
-        <v>1115.5</v>
+        <v>1599.8</v>
       </c>
       <c r="AH7">
-        <v>0.441879468845761</v>
+        <v>0.5798526640397464</v>
       </c>
       <c r="AI7">
-        <v>0.4228463443242539</v>
+        <v>0.574771592568692</v>
       </c>
       <c r="AJ7">
-        <v>0.4049442770537627</v>
+        <v>0.5661004953998584</v>
       </c>
       <c r="AK7">
-        <v>0.3864006373618761</v>
+        <v>0.5609790307875727</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1344,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mega Financial Holding Co., Ltd. (TWSE:2886)</t>
+          <t>Hua Nan Financial Holdings Co., Ltd. (TWSE:2880)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1353,13 +1344,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.012</v>
+        <v>0.0512</v>
       </c>
       <c r="E8">
-        <v>0.00351</v>
-      </c>
-      <c r="F8">
-        <v>0.07519999999999999</v>
+        <v>0.0487</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1374,28 +1362,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>925.8</v>
+        <v>532.1</v>
       </c>
       <c r="L8">
-        <v>0.4332849721533206</v>
+        <v>0.3389603771181042</v>
       </c>
       <c r="M8">
-        <v>709.1</v>
+        <v>429.6</v>
       </c>
       <c r="N8">
-        <v>0.04068109714469299</v>
+        <v>0.04309056441016279</v>
       </c>
       <c r="O8">
-        <v>0.7659321667746815</v>
+        <v>0.8073670362713775</v>
       </c>
       <c r="P8">
-        <v>709.1</v>
+        <v>429.6</v>
       </c>
       <c r="Q8">
-        <v>0.04068109714469299</v>
+        <v>0.04309056441016279</v>
       </c>
       <c r="R8">
-        <v>0.7659321667746815</v>
+        <v>0.8073670362713775</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1404,55 +1392,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>5223.4</v>
+        <v>1232.4</v>
       </c>
       <c r="V8">
-        <v>0.2996666800530099</v>
+        <v>0.1236145520928413</v>
       </c>
       <c r="W8">
-        <v>0.08378962992460924</v>
+        <v>0.07489724677664547</v>
       </c>
       <c r="X8">
-        <v>0.06918615418698497</v>
+        <v>0.100947520212866</v>
       </c>
       <c r="Y8">
-        <v>0.01460347573762427</v>
+        <v>-0.02605027343622053</v>
       </c>
       <c r="Z8">
-        <v>0.08523581763276833</v>
+        <v>0.08282183018412004</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0435205254851293</v>
+        <v>0.06890159084822294</v>
       </c>
       <c r="AC8">
-        <v>-0.0435205254851293</v>
+        <v>-0.06890159084822294</v>
       </c>
       <c r="AD8">
-        <v>21581.6</v>
+        <v>12681</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>21581.6</v>
+        <v>12681</v>
       </c>
       <c r="AG8">
-        <v>16358.2</v>
+        <v>11448.6</v>
       </c>
       <c r="AH8">
-        <v>0.5531998882403754</v>
+        <v>0.559850247453721</v>
       </c>
       <c r="AI8">
-        <v>0.6500325293366424</v>
+        <v>0.6939025658143135</v>
       </c>
       <c r="AJ8">
-        <v>0.4841294034431425</v>
+        <v>0.5345242152738545</v>
       </c>
       <c r="AK8">
-        <v>0.584693359640281</v>
+        <v>0.6717676397242189</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1469,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hua Nan Financial Holdings Co., Ltd. (TWSE:2880)</t>
+          <t>Taichung Commercial Bank Co., Ltd. (TWSE:2812)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1478,10 +1466,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0503</v>
+        <v>0.051</v>
       </c>
       <c r="E9">
-        <v>0.0504</v>
+        <v>0.0745</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1496,28 +1484,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>643.3</v>
+        <v>162.8</v>
       </c>
       <c r="L9">
-        <v>0.3656567953163189</v>
+        <v>0.3908763505402161</v>
       </c>
       <c r="M9">
-        <v>118.7469</v>
+        <v>35.7</v>
       </c>
       <c r="N9">
-        <v>0.01177507288340638</v>
+        <v>0.01708379193185625</v>
       </c>
       <c r="O9">
-        <v>0.1845902378361573</v>
+        <v>0.2192874692874693</v>
       </c>
       <c r="P9">
-        <v>118.7469</v>
+        <v>35.7</v>
       </c>
       <c r="Q9">
-        <v>0.01177507288340638</v>
+        <v>0.01708379193185625</v>
       </c>
       <c r="R9">
-        <v>0.1845902378361573</v>
+        <v>0.2192874692874693</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1526,55 +1514,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>1214.8</v>
+        <v>577.2</v>
       </c>
       <c r="V9">
-        <v>0.1204609007794062</v>
+        <v>0.2762118964444658</v>
       </c>
       <c r="W9">
-        <v>0.1006650496831234</v>
+        <v>0.07529368236055871</v>
       </c>
       <c r="X9">
-        <v>0.07043567002297028</v>
+        <v>0.08346170223820307</v>
       </c>
       <c r="Y9">
-        <v>0.0302293796601531</v>
+        <v>-0.008168019877644359</v>
       </c>
       <c r="Z9">
-        <v>0.1166281066245931</v>
+        <v>0.1504968383017164</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04354577512471471</v>
+        <v>0.06915212854552172</v>
       </c>
       <c r="AC9">
-        <v>-0.04354577512471471</v>
+        <v>-0.06915212854552172</v>
       </c>
       <c r="AD9">
-        <v>13065.8</v>
+        <v>1175.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>13065.8</v>
+        <v>1175.2</v>
       </c>
       <c r="AG9">
-        <v>11851</v>
+        <v>598</v>
       </c>
       <c r="AH9">
-        <v>0.5643876563687884</v>
+        <v>0.3599497687524886</v>
       </c>
       <c r="AI9">
-        <v>0.6477742026643134</v>
+        <v>0.3655934048841188</v>
       </c>
       <c r="AJ9">
-        <v>0.5402633162530316</v>
+        <v>0.2224950701343156</v>
       </c>
       <c r="AK9">
-        <v>0.6252011289599325</v>
+        <v>0.2267470519091495</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1591,7 +1579,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Far Eastern International Bank Ltd. (TWSE:2845)</t>
+          <t>EnTie Commercial Bank Co., Ltd. (TWSE:2849)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1600,10 +1588,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.016</v>
+        <v>-0.00788</v>
       </c>
       <c r="E10">
-        <v>-0.0599</v>
+        <v>0.008369999999999999</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1618,85 +1606,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>86.3</v>
+        <v>65.2</v>
       </c>
       <c r="L10">
-        <v>0.2497829232995658</v>
+        <v>0.3860272350503257</v>
       </c>
       <c r="M10">
-        <v>38.654</v>
+        <v>45.326</v>
       </c>
       <c r="N10">
-        <v>0.02838240693149276</v>
+        <v>0.04822427917863602</v>
       </c>
       <c r="O10">
-        <v>0.4479026651216686</v>
+        <v>0.6951840490797546</v>
       </c>
       <c r="P10">
-        <v>38.654</v>
+        <v>45</v>
       </c>
       <c r="Q10">
-        <v>0.02838240693149276</v>
+        <v>0.04787743376954996</v>
       </c>
       <c r="R10">
-        <v>0.4479026651216686</v>
+        <v>0.6901840490797546</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>0.3260000000000005</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>0.007192339937342817</v>
       </c>
       <c r="U10">
-        <v>1374</v>
+        <v>219.7</v>
       </c>
       <c r="V10">
-        <v>1.008884646449813</v>
+        <v>0.2337482710926694</v>
       </c>
       <c r="W10">
-        <v>0.05160557316271004</v>
+        <v>0.05253404238175812</v>
       </c>
       <c r="X10">
-        <v>0.07221050206084532</v>
+        <v>0.07904972149464126</v>
       </c>
       <c r="Y10">
-        <v>-0.02060492889813528</v>
+        <v>-0.02651567911288314</v>
       </c>
       <c r="Z10">
-        <v>0.1392415266191109</v>
+        <v>0.1129864135342873</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04357954111054031</v>
+        <v>0.06925595111250811</v>
       </c>
       <c r="AC10">
-        <v>-0.04357954111054031</v>
+        <v>-0.06925595111250811</v>
       </c>
       <c r="AD10">
-        <v>1875.7</v>
+        <v>360.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1875.7</v>
+        <v>360.3</v>
       </c>
       <c r="AG10">
-        <v>501.7</v>
+        <v>140.6</v>
       </c>
       <c r="AH10">
-        <v>0.5793489004200642</v>
+        <v>0.277111213659437</v>
       </c>
       <c r="AI10">
-        <v>0.5141016856242292</v>
+        <v>0.2580945558739255</v>
       </c>
       <c r="AJ10">
-        <v>0.269210130929384</v>
+        <v>0.1301249421564091</v>
       </c>
       <c r="AK10">
-        <v>0.2205759507584085</v>
+        <v>0.1195273314630621</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1713,7 +1701,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>O-Bank Co., Ltd. (TWSE:2897)</t>
+          <t>Chang Hwa Commercial Bank, Ltd. (TWSE:2801)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1722,10 +1710,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0474</v>
+        <v>-0.006480000000000001</v>
       </c>
       <c r="E11">
-        <v>-0.00258</v>
+        <v>-0.0275</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1740,28 +1728,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>61.3</v>
+        <v>331.9</v>
       </c>
       <c r="L11">
-        <v>0.1970427515268402</v>
+        <v>0.3558867681749946</v>
       </c>
       <c r="M11">
-        <v>19.6</v>
+        <v>165</v>
       </c>
       <c r="N11">
-        <v>0.02491736587846428</v>
+        <v>0.02790084209814333</v>
       </c>
       <c r="O11">
-        <v>0.3197389885807504</v>
+        <v>0.4971376920759265</v>
       </c>
       <c r="P11">
-        <v>19.6</v>
+        <v>165</v>
       </c>
       <c r="Q11">
-        <v>0.02491736587846428</v>
+        <v>0.02790084209814333</v>
       </c>
       <c r="R11">
-        <v>0.3197389885807504</v>
+        <v>0.4971376920759265</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1770,55 +1758,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>775.1</v>
+        <v>5296.4</v>
       </c>
       <c r="V11">
-        <v>0.9853801169590644</v>
+        <v>0.8956001217491291</v>
       </c>
       <c r="W11">
-        <v>0.05916417334234148</v>
+        <v>0.05491578146199411</v>
       </c>
       <c r="X11">
-        <v>0.302023440933069</v>
+        <v>0.09568346776625192</v>
       </c>
       <c r="Y11">
-        <v>-0.2428592675907275</v>
+        <v>-0.04076768630425781</v>
       </c>
       <c r="Z11">
-        <v>0.03363388687078361</v>
+        <v>0.1181658071791493</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04435462149040321</v>
+        <v>0.07130346153022768</v>
       </c>
       <c r="AC11">
-        <v>-0.04435462149040321</v>
+        <v>-0.07130346153022768</v>
       </c>
       <c r="AD11">
-        <v>9399.4</v>
+        <v>6258.8</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>9399.4</v>
+        <v>6258.8</v>
       </c>
       <c r="AG11">
-        <v>8624.299999999999</v>
+        <v>962.4000000000005</v>
       </c>
       <c r="AH11">
-        <v>0.9227763597094051</v>
+        <v>0.5141711713191923</v>
       </c>
       <c r="AI11">
-        <v>0.8273100146108754</v>
+        <v>0.5441441128141817</v>
       </c>
       <c r="AJ11">
-        <v>0.916416070726498</v>
+        <v>0.13996102498473</v>
       </c>
       <c r="AK11">
-        <v>0.8146661250861963</v>
+        <v>0.1550832299337706</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1835,7 +1823,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chang Hwa Commercial Bank, Ltd. (TWSE:2801)</t>
+          <t>The Shanghai Commercial &amp; Savings Bank, Ltd. (TWSE:5876)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1844,10 +1832,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0228</v>
+        <v>0.0393</v>
       </c>
       <c r="E12">
-        <v>-0.07049999999999999</v>
+        <v>0.0574</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1862,28 +1850,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>293.2</v>
+        <v>514.2</v>
       </c>
       <c r="L12">
-        <v>0.3122470713525026</v>
+        <v>0.4026624902114331</v>
       </c>
       <c r="M12">
-        <v>134.3</v>
+        <v>253.5</v>
       </c>
       <c r="N12">
-        <v>0.02089134323714708</v>
+        <v>0.03645069450435683</v>
       </c>
       <c r="O12">
-        <v>0.4580491132332879</v>
+        <v>0.4929988331388565</v>
       </c>
       <c r="P12">
-        <v>134.3</v>
+        <v>253.5</v>
       </c>
       <c r="Q12">
-        <v>0.02089134323714708</v>
+        <v>0.03645069450435683</v>
       </c>
       <c r="R12">
-        <v>0.4580491132332879</v>
+        <v>0.4929988331388565</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1892,55 +1880,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>3992.1</v>
+        <v>2082.8</v>
       </c>
       <c r="V12">
-        <v>0.6210002333359259</v>
+        <v>0.2994852327955598</v>
       </c>
       <c r="W12">
-        <v>0.05189747946757292</v>
+        <v>0.09188706218727663</v>
       </c>
       <c r="X12">
-        <v>0.06202166811771274</v>
+        <v>0.08587185696398847</v>
       </c>
       <c r="Y12">
-        <v>-0.01012418865013982</v>
+        <v>0.006015205223288161</v>
       </c>
       <c r="Z12">
-        <v>0.1272616385444196</v>
+        <v>0.1261335474739214</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.04510500693484049</v>
+        <v>0.07215887094608762</v>
       </c>
       <c r="AC12">
-        <v>-0.04510500693484049</v>
+        <v>-0.07215887094608762</v>
       </c>
       <c r="AD12">
-        <v>5840.6</v>
+        <v>4591.3</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>5840.6</v>
+        <v>4591.3</v>
       </c>
       <c r="AG12">
-        <v>1848.5</v>
+        <v>2508.5</v>
       </c>
       <c r="AH12">
-        <v>0.4760414374322485</v>
+        <v>0.3976563108982409</v>
       </c>
       <c r="AI12">
-        <v>0.4914509777523476</v>
+        <v>0.4112299369446833</v>
       </c>
       <c r="AJ12">
-        <v>0.2233297088317024</v>
+        <v>0.2650822669104205</v>
       </c>
       <c r="AK12">
-        <v>0.2342156278904756</v>
+        <v>0.2762056815679366</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1957,7 +1945,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Shanghai Commercial &amp; Savings Bank, Ltd. (TWSE:5876)</t>
+          <t>First Financial Holding Co., Ltd. (TWSE:2892)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1966,10 +1954,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0319</v>
+        <v>0.0561</v>
       </c>
       <c r="E13">
-        <v>0.0385</v>
+        <v>0.00907</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1984,28 +1972,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>504.4</v>
+        <v>618</v>
       </c>
       <c r="L13">
-        <v>0.383924493834678</v>
+        <v>0.3172647466502387</v>
       </c>
       <c r="M13">
-        <v>311.1</v>
+        <v>407.8</v>
       </c>
       <c r="N13">
-        <v>0.04085357846355877</v>
+        <v>0.03575123174302597</v>
       </c>
       <c r="O13">
-        <v>0.6167724028548771</v>
+        <v>0.6598705501618123</v>
       </c>
       <c r="P13">
-        <v>311.1</v>
+        <v>407.8</v>
       </c>
       <c r="Q13">
-        <v>0.04085357846355877</v>
+        <v>0.03575123174302597</v>
       </c>
       <c r="R13">
-        <v>0.6167724028548771</v>
+        <v>0.6598705501618123</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2014,55 +2002,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>2022.7</v>
+        <v>1350.6</v>
       </c>
       <c r="V13">
-        <v>0.2656204858831254</v>
+        <v>0.1184051338698648</v>
       </c>
       <c r="W13">
-        <v>0.09557374564195846</v>
+        <v>0.07712852257694132</v>
       </c>
       <c r="X13">
-        <v>0.06098062636472479</v>
+        <v>0.08373128810297115</v>
       </c>
       <c r="Y13">
-        <v>0.03459311927723367</v>
+        <v>-0.006602765526029827</v>
       </c>
       <c r="Z13">
-        <v>0.1556030357870401</v>
+        <v>0.09142537982436789</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.04544514294794733</v>
+        <v>0.07249903310670619</v>
       </c>
       <c r="AC13">
-        <v>-0.04544514294794733</v>
+        <v>-0.07249903310670619</v>
       </c>
       <c r="AD13">
-        <v>6553.9</v>
+        <v>6539.6</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>6553.9</v>
+        <v>6539.6</v>
       </c>
       <c r="AG13">
-        <v>4531.2</v>
+        <v>5189</v>
       </c>
       <c r="AH13">
-        <v>0.4625553148091948</v>
+        <v>0.3644002630083249</v>
       </c>
       <c r="AI13">
-        <v>0.4682695055730208</v>
+        <v>0.4887995276143778</v>
       </c>
       <c r="AJ13">
-        <v>0.373054947226293</v>
+        <v>0.3126732386897732</v>
       </c>
       <c r="AK13">
-        <v>0.3784420335245922</v>
+        <v>0.4313992833567504</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2079,7 +2067,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>E.SUN Financial Holding Company, Ltd. (TWSE:2884)</t>
+          <t>Taiwan Business Bank, Ltd. (TWSE:2834)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2088,13 +2076,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.08039999999999999</v>
+        <v>0.0493</v>
       </c>
       <c r="E14">
-        <v>0.0873</v>
-      </c>
-      <c r="F14">
-        <v>0.121</v>
+        <v>0.0706</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2109,28 +2094,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>717.2</v>
+        <v>260.9</v>
       </c>
       <c r="L14">
-        <v>0.3639685359045928</v>
+        <v>0.3453799311622981</v>
       </c>
       <c r="M14">
-        <v>275.4</v>
+        <v>23.6</v>
       </c>
       <c r="N14">
-        <v>0.02039199425410764</v>
+        <v>0.006972346962892933</v>
       </c>
       <c r="O14">
-        <v>0.3839933073061907</v>
+        <v>0.09045611345343045</v>
       </c>
       <c r="P14">
-        <v>275.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q14">
-        <v>0.02039199425410764</v>
+        <v>0.006972346962892933</v>
       </c>
       <c r="R14">
-        <v>0.3839933073061907</v>
+        <v>0.09045611345343045</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2139,55 +2124,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>2136.6</v>
+        <v>807.3</v>
       </c>
       <c r="V14">
-        <v>0.1582045567295803</v>
+        <v>0.2385074450484519</v>
       </c>
       <c r="W14">
-        <v>0.1174159326806588</v>
+        <v>0.07171917092748363</v>
       </c>
       <c r="X14">
-        <v>0.05726330338560813</v>
+        <v>0.09560802211005445</v>
       </c>
       <c r="Y14">
-        <v>0.06015262929505066</v>
+        <v>-0.02388885118257082</v>
       </c>
       <c r="Z14">
-        <v>0.1446164233764137</v>
+        <v>0.09942875194145366</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.04569587970386488</v>
+        <v>0.07290302456882269</v>
       </c>
       <c r="AC14">
-        <v>-0.04569587970386488</v>
+        <v>-0.07290302456882269</v>
       </c>
       <c r="AD14">
-        <v>9313.9</v>
+        <v>3571.9</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>9313.9</v>
+        <v>3571.9</v>
       </c>
       <c r="AG14">
-        <v>7177.299999999999</v>
+        <v>2764.6</v>
       </c>
       <c r="AH14">
-        <v>0.408160671715047</v>
+        <v>0.5134474679086348</v>
       </c>
       <c r="AI14">
-        <v>0.5775381505435019</v>
+        <v>0.5329603103551179</v>
       </c>
       <c r="AJ14">
-        <v>0.3470211675514684</v>
+        <v>0.4495723159983088</v>
       </c>
       <c r="AK14">
-        <v>0.5130197351021779</v>
+        <v>0.468997574091981</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2213,10 +2198,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0667</v>
+        <v>0.0398</v>
       </c>
       <c r="E15">
-        <v>0.08199999999999999</v>
+        <v>0.0547</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2231,28 +2216,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>736.7</v>
+        <v>612.3</v>
       </c>
       <c r="L15">
-        <v>0.3985824811989396</v>
+        <v>0.3769855929072774</v>
       </c>
       <c r="M15">
-        <v>407.1</v>
+        <v>427.8</v>
       </c>
       <c r="N15">
-        <v>0.03262149925878441</v>
+        <v>0.03608269161022596</v>
       </c>
       <c r="O15">
-        <v>0.5525994298900502</v>
+        <v>0.6986771190592848</v>
       </c>
       <c r="P15">
-        <v>407.1</v>
+        <v>427.8</v>
       </c>
       <c r="Q15">
-        <v>0.03262149925878441</v>
+        <v>0.03608269161022596</v>
       </c>
       <c r="R15">
-        <v>0.5525994298900502</v>
+        <v>0.6986771190592848</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2261,55 +2246,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>2356.5</v>
+        <v>2514.7</v>
       </c>
       <c r="V15">
-        <v>0.1888296806763091</v>
+        <v>0.212101787265627</v>
       </c>
       <c r="W15">
-        <v>0.09446930741315415</v>
+        <v>0.07283562914852615</v>
       </c>
       <c r="X15">
-        <v>0.06431792879836751</v>
+        <v>0.08834278774147364</v>
       </c>
       <c r="Y15">
-        <v>0.03015137861478664</v>
+        <v>-0.01550715859294749</v>
       </c>
       <c r="Z15">
-        <v>0.08839987756117158</v>
+        <v>0.08735686586671114</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.04649581169789355</v>
+        <v>0.07303594263244953</v>
       </c>
       <c r="AC15">
-        <v>-0.04649581169789355</v>
+        <v>-0.07303594263244953</v>
       </c>
       <c r="AD15">
-        <v>12656.5</v>
+        <v>9016</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>12656.5</v>
+        <v>9016</v>
       </c>
       <c r="AG15">
-        <v>10300</v>
+        <v>6501.3</v>
       </c>
       <c r="AH15">
-        <v>0.5035208465945258</v>
+        <v>0.4319642010147518</v>
       </c>
       <c r="AI15">
-        <v>0.5940596383025661</v>
+        <v>0.5810139389213608</v>
       </c>
       <c r="AJ15">
-        <v>0.4521609341732698</v>
+        <v>0.3541514593569896</v>
       </c>
       <c r="AK15">
-        <v>0.5435757786854966</v>
+        <v>0.4999846189340921</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2326,7 +2311,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Taiwan Business Bank, Ltd. (TWSE:2834)</t>
+          <t>E.SUN Financial Holding Company, Ltd. (TWSE:2884)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2335,10 +2320,13 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.00649</v>
+        <v>0.0533</v>
       </c>
       <c r="E16">
-        <v>-0.00621</v>
+        <v>0.0312</v>
+      </c>
+      <c r="F16">
+        <v>-0.0408</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2353,28 +2341,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>184.5</v>
+        <v>513.4</v>
       </c>
       <c r="L16">
-        <v>0.274023466508243</v>
+        <v>0.312819887886912</v>
       </c>
       <c r="M16">
-        <v>23.2296</v>
+        <v>281.5</v>
       </c>
       <c r="N16">
-        <v>0.008405253826392156</v>
+        <v>0.02518948037189158</v>
       </c>
       <c r="O16">
-        <v>0.1259056910569106</v>
+        <v>0.5483054148811843</v>
       </c>
       <c r="P16">
-        <v>23.2296</v>
+        <v>281.5</v>
       </c>
       <c r="Q16">
-        <v>0.008405253826392156</v>
+        <v>0.02518948037189158</v>
       </c>
       <c r="R16">
-        <v>0.1259056910569106</v>
+        <v>0.5483054148811843</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2383,55 +2371,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>1140.4</v>
+        <v>2954.2</v>
       </c>
       <c r="V16">
-        <v>0.4126352353728698</v>
+        <v>0.2643508451674675</v>
       </c>
       <c r="W16">
-        <v>0.05487315230645689</v>
+        <v>0.07541349628367461</v>
       </c>
       <c r="X16">
-        <v>0.08238555460313775</v>
+        <v>0.09457839276752869</v>
       </c>
       <c r="Y16">
-        <v>-0.02751240229668086</v>
+        <v>-0.01916489648385408</v>
       </c>
       <c r="Z16">
-        <v>0.09437902999719652</v>
+        <v>0.1187038912194416</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.04672106545018549</v>
+        <v>0.07360323046718929</v>
       </c>
       <c r="AC16">
-        <v>-0.04672106545018549</v>
+        <v>-0.07360323046718929</v>
       </c>
       <c r="AD16">
-        <v>5100</v>
+        <v>11326.1</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>5100</v>
+        <v>11326.1</v>
       </c>
       <c r="AG16">
-        <v>3959.6</v>
+        <v>8371.900000000001</v>
       </c>
       <c r="AH16">
-        <v>0.6485496649160065</v>
+        <v>0.5033509026105042</v>
       </c>
       <c r="AI16">
-        <v>0.5836709469202774</v>
+        <v>0.6598791649916393</v>
       </c>
       <c r="AJ16">
-        <v>0.5889369803519106</v>
+        <v>0.4282915200130966</v>
       </c>
       <c r="AK16">
-        <v>0.5211782978387344</v>
+        <v>0.5891679627296847</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2448,7 +2436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>First Financial Holding Co., Ltd. (TWSE:2892)</t>
+          <t>SinoPac Financial Holdings Company Limited (TWSE:2890)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2457,10 +2445,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0738</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="E17">
-        <v>0.0275</v>
+        <v>0.15</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2475,28 +2463,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>716.7</v>
+        <v>514.4</v>
       </c>
       <c r="L17">
-        <v>0.3287162317112324</v>
+        <v>0.3633281536940246</v>
       </c>
       <c r="M17">
-        <v>415</v>
+        <v>283.6</v>
       </c>
       <c r="N17">
-        <v>0.03624074332821014</v>
+        <v>0.04565210392453559</v>
       </c>
       <c r="O17">
-        <v>0.5790428352169666</v>
+        <v>0.5513219284603422</v>
       </c>
       <c r="P17">
-        <v>415</v>
+        <v>283.6</v>
       </c>
       <c r="Q17">
-        <v>0.03624074332821014</v>
+        <v>0.04565210392453559</v>
       </c>
       <c r="R17">
-        <v>0.5790428352169666</v>
+        <v>0.5513219284603422</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2505,55 +2493,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>1547.1</v>
+        <v>2247.1</v>
       </c>
       <c r="V17">
-        <v>0.1351037445857202</v>
+        <v>0.3617237049676443</v>
       </c>
       <c r="W17">
-        <v>0.09592579703937683</v>
+        <v>0.08969798423659063</v>
       </c>
       <c r="X17">
-        <v>0.07044327641832969</v>
+        <v>0.1162703772380075</v>
       </c>
       <c r="Y17">
-        <v>0.02548252062104714</v>
+        <v>-0.02657239300141689</v>
       </c>
       <c r="Z17">
-        <v>0.1040279023608222</v>
+        <v>0.1078745856985028</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.04700695186612357</v>
+        <v>0.07480379725299188</v>
       </c>
       <c r="AC17">
-        <v>-0.04700695186612357</v>
+        <v>-0.07480379725299188</v>
       </c>
       <c r="AD17">
-        <v>14840.4</v>
+        <v>11764.4</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>14840.4</v>
+        <v>11764.4</v>
       </c>
       <c r="AG17">
-        <v>13293.3</v>
+        <v>9517.299999999999</v>
       </c>
       <c r="AH17">
-        <v>0.5644540461592296</v>
+        <v>0.6544285348731128</v>
       </c>
       <c r="AI17">
-        <v>0.6493852010676935</v>
+        <v>0.7168781153644596</v>
       </c>
       <c r="AJ17">
-        <v>0.5372224130614884</v>
+        <v>0.6050605550081057</v>
       </c>
       <c r="AK17">
-        <v>0.6239257670410543</v>
+        <v>0.6719596145020651</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2570,7 +2558,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SinoPac Financial Holdings Company Limited (TWSE:2890)</t>
+          <t>Taishin Financial Holding Co., Ltd. (TWSE:2887)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2579,10 +2567,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.0709</v>
+        <v>0.0483</v>
       </c>
       <c r="E18">
-        <v>0.123</v>
+        <v>-0.0214</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2597,28 +2585,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>567.5</v>
+        <v>338.8</v>
       </c>
       <c r="L18">
-        <v>0.3706485533276729</v>
+        <v>0.2498156614068721</v>
       </c>
       <c r="M18">
-        <v>283.4</v>
+        <v>272.4</v>
       </c>
       <c r="N18">
-        <v>0.04318410386127449</v>
+        <v>0.04628323846741993</v>
       </c>
       <c r="O18">
-        <v>0.4993832599118943</v>
+        <v>0.8040141676505312</v>
       </c>
       <c r="P18">
-        <v>283.4</v>
+        <v>272.4</v>
       </c>
       <c r="Q18">
-        <v>0.04318410386127449</v>
+        <v>0.04628323846741993</v>
       </c>
       <c r="R18">
-        <v>0.4993832599118943</v>
+        <v>0.8040141676505312</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2627,55 +2615,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>1111.3</v>
+        <v>1658.3</v>
       </c>
       <c r="V18">
-        <v>0.1693383719867126</v>
+        <v>0.2817602582618299</v>
       </c>
       <c r="W18">
-        <v>0.1089816219537956</v>
+        <v>0.0504895459219409</v>
       </c>
       <c r="X18">
-        <v>0.07055978478692713</v>
+        <v>0.1233786127558041</v>
       </c>
       <c r="Y18">
-        <v>0.03842183716686849</v>
+        <v>-0.0728890668338632</v>
       </c>
       <c r="Z18">
-        <v>0.1302764471142801</v>
+        <v>0.08312188185685042</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.04701546102657871</v>
+        <v>0.07505272327048165</v>
       </c>
       <c r="AC18">
-        <v>-0.04701546102657871</v>
+        <v>-0.07505272327048165</v>
       </c>
       <c r="AD18">
-        <v>8540.1</v>
+        <v>12843.4</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>8540.1</v>
+        <v>12843.4</v>
       </c>
       <c r="AG18">
-        <v>7428.8</v>
+        <v>11185.1</v>
       </c>
       <c r="AH18">
-        <v>0.5654684261754521</v>
+        <v>0.6857530340810191</v>
       </c>
       <c r="AI18">
-        <v>0.5982598827312275</v>
+        <v>0.6783927826284459</v>
       </c>
       <c r="AJ18">
-        <v>0.5309547293337336</v>
+        <v>0.6552259440207141</v>
       </c>
       <c r="AK18">
-        <v>0.5643441003980674</v>
+        <v>0.6475182067640011</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2692,7 +2680,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Taishin Financial Holding Co., Ltd. (TWSE:2887)</t>
+          <t>CTBC Financial Holding Co., Ltd. (TWSE:2891)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2701,46 +2689,49 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.05</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="E19">
-        <v>0.124</v>
+        <v>0.0231</v>
+      </c>
+      <c r="F19">
+        <v>-0.00315</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>0.4054979615608619</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>0.4054979615608619</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>-0.007326732673267326</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>-0.005359303168237383</v>
       </c>
       <c r="K19">
-        <v>736.4</v>
+        <v>1255.7</v>
       </c>
       <c r="L19">
-        <v>0.4942945361793529</v>
+        <v>0.146266744321491</v>
       </c>
       <c r="M19">
-        <v>217.7</v>
+        <v>783.2799</v>
       </c>
       <c r="N19">
-        <v>0.02792851736391743</v>
+        <v>0.05421372508305648</v>
       </c>
       <c r="O19">
-        <v>0.2956273764258555</v>
+        <v>0.6237794855459107</v>
       </c>
       <c r="P19">
-        <v>217.7</v>
+        <v>783.2799</v>
       </c>
       <c r="Q19">
-        <v>0.02792851736391743</v>
+        <v>0.05421372508305648</v>
       </c>
       <c r="R19">
-        <v>0.2956273764258555</v>
+        <v>0.6237794855459107</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2749,61 +2740,73 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>1562.5</v>
+        <v>14998.5</v>
       </c>
       <c r="V19">
-        <v>0.2004515773133716</v>
+        <v>1.038102159468439</v>
       </c>
       <c r="W19">
-        <v>0.1220215410107705</v>
+        <v>0.08533991205714248</v>
       </c>
       <c r="X19">
-        <v>0.07277449090328397</v>
+        <v>0.09329362408039482</v>
       </c>
       <c r="Y19">
-        <v>0.04924705010748653</v>
+        <v>-0.007953712023252346</v>
       </c>
       <c r="Z19">
-        <v>0.09565144812619981</v>
+        <v>0.8175723292002363</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>-0.004381617974146043</v>
       </c>
       <c r="AB19">
-        <v>0.04716999343211176</v>
+        <v>0.07349832038118259</v>
       </c>
       <c r="AC19">
-        <v>-0.04716999343211176</v>
+        <v>-0.07787993835532864</v>
       </c>
       <c r="AD19">
-        <v>10937.9</v>
+        <v>13889.7</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>10937.9</v>
+        <v>13889.7</v>
       </c>
       <c r="AG19">
-        <v>9375.4</v>
+        <v>-1108.799999999999</v>
       </c>
       <c r="AH19">
-        <v>0.583890288691493</v>
+        <v>0.4901491652462974</v>
       </c>
       <c r="AI19">
-        <v>0.6097987946635148</v>
+        <v>0.5569201530059903</v>
       </c>
       <c r="AJ19">
-        <v>0.5460242395298859</v>
+        <v>-0.08312342569269515</v>
       </c>
       <c r="AK19">
-        <v>0.5725644909126442</v>
+        <v>-0.1115302211895349</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>703.7</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>703.7</v>
+      </c>
+      <c r="AN19">
+        <v>1521.325301204819</v>
+      </c>
+      <c r="AO19">
+        <v>-0.08938468097200511</v>
+      </c>
+      <c r="AP19">
+        <v>-121.44578313253</v>
+      </c>
+      <c r="AQ19">
+        <v>-0.08938468097200511</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/taiwan/taiwan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_bank_money_center.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0398</v>
+        <v>0.0613</v>
       </c>
       <c r="E2">
-        <v>0.0312</v>
+        <v>0.0607</v>
       </c>
       <c r="F2">
-        <v>-0.00315</v>
+        <v>0.143</v>
       </c>
       <c r="G2">
-        <v>0.141702860352751</v>
+        <v>0.02195164483469591</v>
       </c>
       <c r="H2">
-        <v>0.141702860352751</v>
+        <v>0.02195164483469591</v>
       </c>
       <c r="I2">
-        <v>-0.0006777381611011258</v>
+        <v>0.124489558046626</v>
       </c>
       <c r="J2">
-        <v>-0.0005562187959479574</v>
+        <v>0.1058873947787764</v>
       </c>
       <c r="K2">
-        <v>6634.7</v>
+        <v>8328.809999999999</v>
       </c>
       <c r="L2">
-        <v>0.2700666343738933</v>
+        <v>0.2847836121739309</v>
       </c>
       <c r="M2">
-        <v>4123.2059</v>
+        <v>3049.8723</v>
       </c>
       <c r="N2">
-        <v>0.03772071324541117</v>
+        <v>0.02390828476351365</v>
       </c>
       <c r="O2">
-        <v>0.6214607894855834</v>
+        <v>0.3661834403714336</v>
       </c>
       <c r="P2">
-        <v>4111.8799</v>
+        <v>2882.7823</v>
       </c>
       <c r="Q2">
-        <v>0.03761709853186569</v>
+        <v>0.02259844785619936</v>
       </c>
       <c r="R2">
-        <v>0.6197537040107315</v>
+        <v>0.3461217508863811</v>
       </c>
       <c r="S2">
-        <v>11.326</v>
+        <v>167.09</v>
       </c>
       <c r="T2">
-        <v>0.002746891684453595</v>
+        <v>0.0547859003801569</v>
       </c>
       <c r="U2">
-        <v>40647.7</v>
+        <v>35206.3</v>
       </c>
       <c r="V2">
-        <v>0.3718611859246465</v>
+        <v>0.2759860620622347</v>
       </c>
       <c r="W2">
-        <v>0.07171917092748363</v>
+        <v>0.106514657980456</v>
       </c>
       <c r="X2">
-        <v>0.09568346776625192</v>
+        <v>0.07774831311653563</v>
       </c>
       <c r="Y2">
-        <v>-0.02396429683876829</v>
+        <v>0.02876634486392039</v>
       </c>
       <c r="Z2">
-        <v>0.1287045540697215</v>
+        <v>0.1769280365625745</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07215887094608762</v>
+        <v>0.06177288753711747</v>
       </c>
       <c r="AC2">
-        <v>-0.07130346153022768</v>
+        <v>-0.0601211766328185</v>
       </c>
       <c r="AD2">
-        <v>129940.7</v>
+        <v>138670.9</v>
       </c>
       <c r="AE2">
-        <v>128.7496281497762</v>
+        <v>109.3296820628648</v>
       </c>
       <c r="AF2">
-        <v>130069.4496281498</v>
+        <v>138780.2296820629</v>
       </c>
       <c r="AG2">
-        <v>89421.74962814979</v>
+        <v>103573.9296820629</v>
       </c>
       <c r="AH2">
-        <v>0.5433636925251133</v>
+        <v>0.5210529556742846</v>
       </c>
       <c r="AI2">
-        <v>0.6186381762685859</v>
+        <v>0.6047249862090748</v>
       </c>
       <c r="AJ2">
-        <v>0.4499647879778388</v>
+        <v>0.4481015196088827</v>
       </c>
       <c r="AK2">
-        <v>0.5272398474218496</v>
+        <v>0.5330980481361219</v>
       </c>
       <c r="AL2">
-        <v>703.7</v>
+        <v>2394.1</v>
       </c>
       <c r="AM2">
-        <v>703.7</v>
+        <v>2394.1</v>
       </c>
       <c r="AN2">
-        <v>1601.635646493282</v>
+        <v>36.84332323715394</v>
       </c>
       <c r="AO2">
-        <v>-0.08938468097200511</v>
+        <v>1.504197819639948</v>
       </c>
       <c r="AP2">
-        <v>1102.203249453344</v>
+        <v>27.51844669803466</v>
       </c>
       <c r="AQ2">
-        <v>-0.08938468097200511</v>
+        <v>1.504197819639948</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Union Bank of Taiwan (TWSE:2838)</t>
+          <t>CTBC Financial Holding Co., Ltd. (TWSE:2891)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,46 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.049</v>
+        <v>-0.0309</v>
       </c>
       <c r="E3">
-        <v>0.0433</v>
+        <v>0.0495</v>
+      </c>
+      <c r="F3">
+        <v>0.31</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.05703472721942379</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.05703472721942379</v>
       </c>
       <c r="I3">
-        <v>0.09677772414740479</v>
+        <v>0.3199275072625996</v>
       </c>
       <c r="J3">
-        <v>0.07439425351750353</v>
+        <v>0.2781095256421736</v>
       </c>
       <c r="K3">
-        <v>102.7</v>
+        <v>1481.6</v>
       </c>
       <c r="L3">
-        <v>0.2148985143335426</v>
+        <v>0.1316240682995301</v>
       </c>
       <c r="M3">
-        <v>30.6</v>
+        <v>622.5822999999999</v>
       </c>
       <c r="N3">
-        <v>0.01634790041671119</v>
+        <v>0.03350206636030004</v>
       </c>
       <c r="O3">
-        <v>0.2979552093476144</v>
+        <v>0.4202094357451404</v>
       </c>
       <c r="P3">
-        <v>30.6</v>
+        <v>622.5822999999999</v>
       </c>
       <c r="Q3">
-        <v>0.01634790041671119</v>
+        <v>0.03350206636030004</v>
       </c>
       <c r="R3">
-        <v>0.2979552093476144</v>
+        <v>0.4202094357451404</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,67 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>272</v>
+        <v>14484.7</v>
       </c>
       <c r="V3">
-        <v>0.1453146703707661</v>
+        <v>0.779442943702444</v>
       </c>
       <c r="W3">
-        <v>0.04618844164605352</v>
+        <v>0.1450614866452573</v>
       </c>
       <c r="X3">
-        <v>0.105719982515143</v>
+        <v>0.07587959904606612</v>
       </c>
       <c r="Y3">
-        <v>-0.0595315408690895</v>
+        <v>0.06918188759919117</v>
       </c>
       <c r="Z3">
-        <v>0.08905329093059398</v>
+        <v>1.294512040849185</v>
       </c>
       <c r="AA3">
-        <v>0.006625053102058608</v>
+        <v>0.3600161296186489</v>
       </c>
       <c r="AB3">
-        <v>0.07432694948498544</v>
+        <v>0.06269427417774805</v>
       </c>
       <c r="AC3">
-        <v>-0.06770189638292684</v>
+        <v>0.2973218554409009</v>
       </c>
       <c r="AD3">
-        <v>2614.6</v>
+        <v>16724.5</v>
       </c>
       <c r="AE3">
-        <v>128.7496281497762</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>2743.349628149776</v>
+        <v>16724.5</v>
       </c>
       <c r="AG3">
-        <v>2471.349628149776</v>
+        <v>2239.799999999999</v>
       </c>
       <c r="AH3">
-        <v>0.5944226838100569</v>
+        <v>0.4736758629088674</v>
       </c>
       <c r="AI3">
-        <v>0.5894289836878285</v>
+        <v>0.5522589635382614</v>
       </c>
       <c r="AJ3">
-        <v>0.569022446781921</v>
+        <v>0.1075627185062814</v>
       </c>
       <c r="AK3">
-        <v>0.563945424805296</v>
+        <v>0.1417675690387427</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>2394.1</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>2394.1</v>
       </c>
       <c r="AN3">
-        <v>36.31388888888889</v>
+        <v>4.517327066958377</v>
+      </c>
+      <c r="AO3">
+        <v>1.504197819639948</v>
       </c>
       <c r="AP3">
-        <v>34.32430039096911</v>
+        <v>0.6049752856332548</v>
+      </c>
+      <c r="AQ3">
+        <v>1.504197819639948</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>O-Bank Co., Ltd. (TWSE:2897)</t>
+          <t>Union Bank of Taiwan (TWSE:2838)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,10 +862,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0374</v>
+        <v>0.0678</v>
       </c>
       <c r="E4">
-        <v>0.106</v>
+        <v>0.0935</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,34 +874,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.07303125776198093</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.06066403868330568</v>
       </c>
       <c r="K4">
-        <v>65.8</v>
+        <v>150</v>
       </c>
       <c r="L4">
-        <v>0.2433431952662722</v>
+        <v>0.2763957987838584</v>
       </c>
       <c r="M4">
-        <v>25.8</v>
+        <v>11.4</v>
       </c>
       <c r="N4">
-        <v>0.03458445040214477</v>
+        <v>0.006418557513653511</v>
       </c>
       <c r="O4">
-        <v>0.39209726443769</v>
+        <v>0.076</v>
       </c>
       <c r="P4">
-        <v>25.8</v>
+        <v>11.4</v>
       </c>
       <c r="Q4">
-        <v>0.03458445040214477</v>
+        <v>0.006418557513653511</v>
       </c>
       <c r="R4">
-        <v>0.39209726443769</v>
+        <v>0.076</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,61 +910,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>600.3</v>
+        <v>330.5</v>
       </c>
       <c r="V4">
-        <v>0.8046916890080429</v>
+        <v>0.1860818647598671</v>
       </c>
       <c r="W4">
-        <v>0.05561189993238674</v>
+        <v>0.08409957389549226</v>
       </c>
       <c r="X4">
-        <v>0.3143380328515837</v>
+        <v>0.09060626201415681</v>
       </c>
       <c r="Y4">
-        <v>-0.2587261329191969</v>
+        <v>-0.006506688118664547</v>
       </c>
       <c r="Z4">
-        <v>0.02737590232148462</v>
+        <v>0.1283091052395196</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.007783748523670558</v>
       </c>
       <c r="AB4">
-        <v>0.06846459864387146</v>
+        <v>0.06349912796742367</v>
       </c>
       <c r="AC4">
-        <v>-0.06846459864387146</v>
+        <v>-0.05571537944375311</v>
       </c>
       <c r="AD4">
-        <v>7408.8</v>
+        <v>3005.7</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>109.3296820628648</v>
       </c>
       <c r="AF4">
-        <v>7408.8</v>
+        <v>3115.029682062865</v>
       </c>
       <c r="AG4">
-        <v>6808.5</v>
+        <v>2784.529682062865</v>
       </c>
       <c r="AH4">
-        <v>0.9085201353803894</v>
+        <v>0.6368732551677266</v>
       </c>
       <c r="AI4">
-        <v>0.8240698515099272</v>
+        <v>0.5957868559941762</v>
       </c>
       <c r="AJ4">
-        <v>0.9012509100536105</v>
+        <v>0.6105581632761214</v>
       </c>
       <c r="AK4">
-        <v>0.811482443803485</v>
+        <v>0.5685115677059093</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>48.87317073170731</v>
+      </c>
+      <c r="AP4">
+        <v>45.27690539939617</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mega Financial Holding Co., Ltd. (TWSE:2886)</t>
+          <t>O-Bank Co., Ltd. (TWSE:2897)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,13 +990,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.004</v>
+        <v>0.109</v>
       </c>
       <c r="E5">
-        <v>-0.061</v>
-      </c>
-      <c r="F5">
-        <v>0.0235</v>
+        <v>0.487</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -996,85 +1008,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>619.3</v>
+        <v>170.1</v>
       </c>
       <c r="L5">
-        <v>0.3645085344320188</v>
+        <v>0.4545697487974345</v>
       </c>
       <c r="M5">
-        <v>537.2</v>
+        <v>35.39</v>
       </c>
       <c r="N5">
-        <v>0.03900809643103511</v>
+        <v>0.03999321957283309</v>
       </c>
       <c r="O5">
-        <v>0.8674309704505088</v>
+        <v>0.2080540858318636</v>
       </c>
       <c r="P5">
-        <v>537.2</v>
+        <v>32.3</v>
       </c>
       <c r="Q5">
-        <v>0.03900809643103511</v>
+        <v>0.03650129958187365</v>
       </c>
       <c r="R5">
-        <v>0.8674309704505088</v>
+        <v>0.1898883009994121</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.090000000000003</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.08731280022605266</v>
       </c>
       <c r="U5">
-        <v>2868.9</v>
+        <v>590.5</v>
       </c>
       <c r="V5">
-        <v>0.2083215336020041</v>
+        <v>0.6673070403435417</v>
       </c>
       <c r="W5">
-        <v>0.0532997108234646</v>
+        <v>0.1729713239780354</v>
       </c>
       <c r="X5">
-        <v>0.1089285381353864</v>
+        <v>0.2038366256865331</v>
       </c>
       <c r="Y5">
-        <v>-0.05562882731192183</v>
+        <v>-0.03086530170849774</v>
       </c>
       <c r="Z5">
-        <v>0.0607275872668654</v>
+        <v>0.04768033027102101</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06883276429938397</v>
+        <v>0.05870402742080873</v>
       </c>
       <c r="AC5">
-        <v>-0.06883276429938397</v>
+        <v>-0.05870402742080873</v>
       </c>
       <c r="AD5">
-        <v>21976.9</v>
+        <v>7361.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>21976.9</v>
+        <v>7361.7</v>
       </c>
       <c r="AG5">
-        <v>19108</v>
+        <v>6771.2</v>
       </c>
       <c r="AH5">
-        <v>0.6147659755401641</v>
+        <v>0.8926951713433414</v>
       </c>
       <c r="AI5">
-        <v>0.7046836973216318</v>
+        <v>0.806867752471558</v>
       </c>
       <c r="AJ5">
-        <v>0.5811523897869493</v>
+        <v>0.8844189600449315</v>
       </c>
       <c r="AK5">
-        <v>0.6747651670315701</v>
+        <v>0.7935030996214829</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1091,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Far Eastern International Bank Ltd. (TWSE:2845)</t>
+          <t>Hua Nan Financial Holdings Co., Ltd. (TWSE:2880)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,10 +1112,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.00607</v>
+        <v>0.0626</v>
       </c>
       <c r="E6">
-        <v>-0.00157</v>
+        <v>0.0766</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1118,28 +1130,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>101.5</v>
+        <v>631</v>
       </c>
       <c r="L6">
-        <v>0.3094512195121951</v>
+        <v>0.3676299230948497</v>
       </c>
       <c r="M6">
-        <v>35.4</v>
+        <v>249.3</v>
       </c>
       <c r="N6">
-        <v>0.02429483220094709</v>
+        <v>0.02504998944946293</v>
       </c>
       <c r="O6">
-        <v>0.3487684729064039</v>
+        <v>0.3950871632329636</v>
       </c>
       <c r="P6">
-        <v>35.4</v>
+        <v>249.3</v>
       </c>
       <c r="Q6">
-        <v>0.02429483220094709</v>
+        <v>0.02504998944946293</v>
       </c>
       <c r="R6">
-        <v>0.3487684729064039</v>
+        <v>0.3950871632329636</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1148,55 +1160,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>874.8</v>
+        <v>1231.9</v>
       </c>
       <c r="V6">
-        <v>0.6003705991352687</v>
+        <v>0.1237829201876991</v>
       </c>
       <c r="W6">
-        <v>0.05725406137184116</v>
+        <v>0.1128034609746505</v>
       </c>
       <c r="X6">
-        <v>0.1073239835436853</v>
+        <v>0.08728975532582872</v>
       </c>
       <c r="Y6">
-        <v>-0.05006992217184415</v>
+        <v>0.02551370564882179</v>
       </c>
       <c r="Z6">
-        <v>0.144207518135854</v>
+        <v>0.1007210793656755</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06884518680129105</v>
+        <v>0.05922858431405595</v>
       </c>
       <c r="AC6">
-        <v>-0.06884518680129105</v>
+        <v>-0.05922858431405595</v>
       </c>
       <c r="AD6">
-        <v>2230.4</v>
+        <v>15540.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2230.4</v>
+        <v>15540.8</v>
       </c>
       <c r="AG6">
-        <v>1355.6</v>
+        <v>14308.9</v>
       </c>
       <c r="AH6">
-        <v>0.6048542372881356</v>
+        <v>0.6096128726037445</v>
       </c>
       <c r="AI6">
-        <v>0.5752011553538271</v>
+        <v>0.7187593944971951</v>
       </c>
       <c r="AJ6">
-        <v>0.481956838624809</v>
+        <v>0.5897901982605828</v>
       </c>
       <c r="AK6">
-        <v>0.4514453177034768</v>
+        <v>0.7017675504418877</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1213,7 +1225,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>King's Town Bank (TWSE:2809)</t>
+          <t>Far Eastern International Bank Ltd. (TWSE:2845)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1222,10 +1234,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.176</v>
+        <v>0.0452</v>
       </c>
       <c r="E7">
-        <v>-0.317</v>
+        <v>0.08220000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1240,85 +1252,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>25.7</v>
+        <v>143.3</v>
       </c>
       <c r="L7">
-        <v>0.2542037586547972</v>
+        <v>0.3685699588477366</v>
       </c>
       <c r="M7">
-        <v>85.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="N7">
-        <v>0.06940140270755178</v>
+        <v>0.05874300678490656</v>
       </c>
       <c r="O7">
-        <v>3.311284046692607</v>
+        <v>0.6887648290300069</v>
       </c>
       <c r="P7">
-        <v>74.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="Q7">
-        <v>0.06043059859729244</v>
+        <v>0.05874300678490656</v>
       </c>
       <c r="R7">
-        <v>2.883268482490272</v>
+        <v>0.6887648290300069</v>
       </c>
       <c r="S7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.1292596944770858</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>92.5</v>
+        <v>1146</v>
       </c>
       <c r="V7">
-        <v>0.07543630729081716</v>
+        <v>0.6820616593262706</v>
       </c>
       <c r="W7">
-        <v>0.01450829852094388</v>
+        <v>0.08699611461874697</v>
       </c>
       <c r="X7">
-        <v>0.1036129486796114</v>
+        <v>0.08138933038391144</v>
       </c>
       <c r="Y7">
-        <v>-0.08910465015866753</v>
+        <v>0.00560678423483553</v>
       </c>
       <c r="Z7">
-        <v>0.03502026395095085</v>
+        <v>0.1294791527907286</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06887652157663122</v>
+        <v>0.0593400940938377</v>
       </c>
       <c r="AC7">
-        <v>-0.06887652157663122</v>
+        <v>-0.0593400940938377</v>
       </c>
       <c r="AD7">
-        <v>1692.3</v>
+        <v>2048.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1692.3</v>
+        <v>2048.9</v>
       </c>
       <c r="AG7">
-        <v>1599.8</v>
+        <v>902.9000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.5798526640397464</v>
+        <v>0.5494355206350058</v>
       </c>
       <c r="AI7">
-        <v>0.574771592568692</v>
+        <v>0.5332344368103269</v>
       </c>
       <c r="AJ7">
-        <v>0.5661004953998584</v>
+        <v>0.3495412488869962</v>
       </c>
       <c r="AK7">
-        <v>0.5609790307875727</v>
+        <v>0.3348538792464026</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1335,7 +1347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hua Nan Financial Holdings Co., Ltd. (TWSE:2880)</t>
+          <t>Mega Financial Holding Co., Ltd. (TWSE:2886)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1344,10 +1356,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0512</v>
+        <v>0.0213</v>
       </c>
       <c r="E8">
-        <v>0.0487</v>
+        <v>0.0366</v>
+      </c>
+      <c r="F8">
+        <v>0.143</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1362,28 +1377,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>532.1</v>
+        <v>985.2</v>
       </c>
       <c r="L8">
-        <v>0.3389603771181042</v>
+        <v>0.4913715710723192</v>
       </c>
       <c r="M8">
-        <v>429.6</v>
+        <v>481.8</v>
       </c>
       <c r="N8">
-        <v>0.04309056441016279</v>
+        <v>0.02679942151518523</v>
       </c>
       <c r="O8">
-        <v>0.8073670362713775</v>
+        <v>0.4890377588306943</v>
       </c>
       <c r="P8">
-        <v>429.6</v>
+        <v>481.8</v>
       </c>
       <c r="Q8">
-        <v>0.04309056441016279</v>
+        <v>0.02679942151518523</v>
       </c>
       <c r="R8">
-        <v>0.8073670362713775</v>
+        <v>0.4890377588306943</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1392,55 +1407,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1232.4</v>
+        <v>2255</v>
       </c>
       <c r="V8">
-        <v>0.1236145520928413</v>
+        <v>0.1254310824340861</v>
       </c>
       <c r="W8">
-        <v>0.07489724677664547</v>
+        <v>0.106970684039088</v>
       </c>
       <c r="X8">
-        <v>0.100947520212866</v>
+        <v>0.07801488265315049</v>
       </c>
       <c r="Y8">
-        <v>-0.02605027343622053</v>
+        <v>0.02895580138593747</v>
       </c>
       <c r="Z8">
-        <v>0.08282183018412004</v>
+        <v>0.0708030228123455</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06890159084822294</v>
+        <v>0.05942081272452453</v>
       </c>
       <c r="AC8">
-        <v>-0.06890159084822294</v>
+        <v>-0.05942081272452453</v>
       </c>
       <c r="AD8">
-        <v>12681</v>
+        <v>18405.5</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>12681</v>
+        <v>18405.5</v>
       </c>
       <c r="AG8">
-        <v>11448.6</v>
+        <v>16150.5</v>
       </c>
       <c r="AH8">
-        <v>0.559850247453721</v>
+        <v>0.5058749158272293</v>
       </c>
       <c r="AI8">
-        <v>0.6939025658143135</v>
+        <v>0.6503963051567375</v>
       </c>
       <c r="AJ8">
-        <v>0.5345242152738545</v>
+        <v>0.4732261892553145</v>
       </c>
       <c r="AK8">
-        <v>0.6717676397242189</v>
+        <v>0.620126017992697</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1457,7 +1472,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Taichung Commercial Bank Co., Ltd. (TWSE:2812)</t>
+          <t>King's Town Bank (TWSE:2809)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1466,10 +1481,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.051</v>
+        <v>0.0394</v>
       </c>
       <c r="E9">
-        <v>0.0745</v>
+        <v>0.0239</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1484,28 +1499,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>162.8</v>
+        <v>174.3</v>
       </c>
       <c r="L9">
-        <v>0.3908763505402161</v>
+        <v>0.602280580511403</v>
       </c>
       <c r="M9">
-        <v>35.7</v>
+        <v>38</v>
       </c>
       <c r="N9">
-        <v>0.01708379193185625</v>
+        <v>0.02622498274672188</v>
       </c>
       <c r="O9">
-        <v>0.2192874692874693</v>
+        <v>0.2180149168100975</v>
       </c>
       <c r="P9">
-        <v>35.7</v>
+        <v>38</v>
       </c>
       <c r="Q9">
-        <v>0.01708379193185625</v>
+        <v>0.02622498274672188</v>
       </c>
       <c r="R9">
-        <v>0.2192874692874693</v>
+        <v>0.2180149168100975</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1514,55 +1529,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>577.2</v>
+        <v>345.7</v>
       </c>
       <c r="V9">
-        <v>0.2762118964444658</v>
+        <v>0.2385783298826777</v>
       </c>
       <c r="W9">
-        <v>0.07529368236055871</v>
+        <v>0.1392172523961661</v>
       </c>
       <c r="X9">
-        <v>0.08346170223820307</v>
+        <v>0.07420188140590672</v>
       </c>
       <c r="Y9">
-        <v>-0.008168019877644359</v>
+        <v>0.06501537099025942</v>
       </c>
       <c r="Z9">
-        <v>0.1504968383017164</v>
+        <v>0.1014797671645978</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06915212854552172</v>
+        <v>0.05953310752901077</v>
       </c>
       <c r="AC9">
-        <v>-0.06915212854552172</v>
+        <v>-0.05953310752901077</v>
       </c>
       <c r="AD9">
-        <v>1175.2</v>
+        <v>1163.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1175.2</v>
+        <v>1163.1</v>
       </c>
       <c r="AG9">
-        <v>598</v>
+        <v>817.3999999999999</v>
       </c>
       <c r="AH9">
-        <v>0.3599497687524886</v>
+        <v>0.4452739175376134</v>
       </c>
       <c r="AI9">
-        <v>0.3655934048841188</v>
+        <v>0.4464532473514509</v>
       </c>
       <c r="AJ9">
-        <v>0.2224950701343156</v>
+        <v>0.3606600776561948</v>
       </c>
       <c r="AK9">
-        <v>0.2267470519091495</v>
+        <v>0.3617614516485947</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1579,7 +1594,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EnTie Commercial Bank Co., Ltd. (TWSE:2849)</t>
+          <t>Taichung Commercial Bank Co., Ltd. (TWSE:2812)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1588,10 +1603,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.00788</v>
+        <v>0.0649</v>
       </c>
       <c r="E10">
-        <v>0.008369999999999999</v>
+        <v>0.0955</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1606,85 +1621,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>65.2</v>
+        <v>195.9</v>
       </c>
       <c r="L10">
-        <v>0.3860272350503257</v>
+        <v>0.4139898562975486</v>
       </c>
       <c r="M10">
-        <v>45.326</v>
+        <v>46.8</v>
       </c>
       <c r="N10">
-        <v>0.04822427917863602</v>
+        <v>0.01725600088492312</v>
       </c>
       <c r="O10">
-        <v>0.6951840490797546</v>
+        <v>0.2388973966309341</v>
       </c>
       <c r="P10">
-        <v>45</v>
+        <v>46.8</v>
       </c>
       <c r="Q10">
-        <v>0.04787743376954996</v>
+        <v>0.01725600088492312</v>
       </c>
       <c r="R10">
-        <v>0.6901840490797546</v>
+        <v>0.2388973966309341</v>
       </c>
       <c r="S10">
-        <v>0.3260000000000005</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>0.007192339937342817</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>219.7</v>
+        <v>446</v>
       </c>
       <c r="V10">
-        <v>0.2337482710926694</v>
+        <v>0.1644482135614468</v>
       </c>
       <c r="W10">
-        <v>0.05253404238175812</v>
+        <v>0.0960623743441377</v>
       </c>
       <c r="X10">
-        <v>0.07904972149464126</v>
+        <v>0.07091816173188349</v>
       </c>
       <c r="Y10">
-        <v>-0.02651567911288314</v>
+        <v>0.0251442126122542</v>
       </c>
       <c r="Z10">
-        <v>0.1129864135342873</v>
+        <v>0.1794259280324574</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06925595111250811</v>
+        <v>0.0596544961299126</v>
       </c>
       <c r="AC10">
-        <v>-0.06925595111250811</v>
+        <v>-0.0596544961299126</v>
       </c>
       <c r="AD10">
-        <v>360.3</v>
+        <v>1660.6</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>360.3</v>
+        <v>1660.6</v>
       </c>
       <c r="AG10">
-        <v>140.6</v>
+        <v>1214.6</v>
       </c>
       <c r="AH10">
-        <v>0.277111213659437</v>
+        <v>0.3797653623619274</v>
       </c>
       <c r="AI10">
-        <v>0.2580945558739255</v>
+        <v>0.4216433069266707</v>
       </c>
       <c r="AJ10">
-        <v>0.1301249421564091</v>
+        <v>0.3093182570606361</v>
       </c>
       <c r="AK10">
-        <v>0.1195273314630621</v>
+        <v>0.3477837590195854</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1701,7 +1716,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chang Hwa Commercial Bank, Ltd. (TWSE:2801)</t>
+          <t>EnTie Commercial Bank Co., Ltd. (TWSE:2849)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1710,10 +1725,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.006480000000000001</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="E11">
-        <v>-0.0275</v>
+        <v>-0.353</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1728,28 +1743,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>331.9</v>
+        <v>6.81</v>
       </c>
       <c r="L11">
-        <v>0.3558867681749946</v>
+        <v>0.06618075801749271</v>
       </c>
       <c r="M11">
-        <v>165</v>
+        <v>24.3</v>
       </c>
       <c r="N11">
-        <v>0.02790084209814333</v>
+        <v>0.02569796954314721</v>
       </c>
       <c r="O11">
-        <v>0.4971376920759265</v>
+        <v>3.568281938325991</v>
       </c>
       <c r="P11">
-        <v>165</v>
+        <v>24.3</v>
       </c>
       <c r="Q11">
-        <v>0.02790084209814333</v>
+        <v>0.02569796954314721</v>
       </c>
       <c r="R11">
-        <v>0.4971376920759265</v>
+        <v>3.568281938325991</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1758,55 +1773,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>5296.4</v>
+        <v>230.4</v>
       </c>
       <c r="V11">
-        <v>0.8956001217491291</v>
+        <v>0.2436548223350254</v>
       </c>
       <c r="W11">
-        <v>0.05491578146199411</v>
+        <v>0.006575263107077338</v>
       </c>
       <c r="X11">
-        <v>0.09568346776625192</v>
+        <v>0.06288792392089979</v>
       </c>
       <c r="Y11">
-        <v>-0.04076768630425781</v>
+        <v>-0.05631266081382245</v>
       </c>
       <c r="Z11">
-        <v>0.1181658071791493</v>
+        <v>0.08875433421311391</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07130346153022768</v>
+        <v>0.0601211766328185</v>
       </c>
       <c r="AC11">
-        <v>-0.07130346153022768</v>
+        <v>-0.0601211766328185</v>
       </c>
       <c r="AD11">
-        <v>6258.8</v>
+        <v>138.7</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>6258.8</v>
+        <v>138.7</v>
       </c>
       <c r="AG11">
-        <v>962.4000000000005</v>
+        <v>-91.70000000000002</v>
       </c>
       <c r="AH11">
-        <v>0.5141711713191923</v>
+        <v>0.1279166282394171</v>
       </c>
       <c r="AI11">
-        <v>0.5441441128141817</v>
+        <v>0.1203470715835141</v>
       </c>
       <c r="AJ11">
-        <v>0.13996102498473</v>
+        <v>-0.1073896240777609</v>
       </c>
       <c r="AK11">
-        <v>0.1550832299337706</v>
+        <v>-0.09944691465133937</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1823,7 +1838,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Shanghai Commercial &amp; Savings Bank, Ltd. (TWSE:5876)</t>
+          <t>Chang Hwa Commercial Bank, Ltd. (TWSE:2801)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1832,10 +1847,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0393</v>
+        <v>0.0304</v>
       </c>
       <c r="E12">
-        <v>0.0574</v>
+        <v>-0.00031</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1850,28 +1865,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>514.2</v>
+        <v>394.3</v>
       </c>
       <c r="L12">
-        <v>0.4026624902114331</v>
+        <v>0.3637453874538745</v>
       </c>
       <c r="M12">
-        <v>253.5</v>
+        <v>181.1</v>
       </c>
       <c r="N12">
-        <v>0.03645069450435683</v>
+        <v>0.02854755824584634</v>
       </c>
       <c r="O12">
-        <v>0.4929988331388565</v>
+        <v>0.4592949530814101</v>
       </c>
       <c r="P12">
-        <v>253.5</v>
+        <v>181.1</v>
       </c>
       <c r="Q12">
-        <v>0.03645069450435683</v>
+        <v>0.02854755824584634</v>
       </c>
       <c r="R12">
-        <v>0.4929988331388565</v>
+        <v>0.4592949530814101</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1880,55 +1895,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2082.8</v>
+        <v>3207.7</v>
       </c>
       <c r="V12">
-        <v>0.2994852327955598</v>
+        <v>0.5056433052744411</v>
       </c>
       <c r="W12">
-        <v>0.09188706218727663</v>
+        <v>0.07520073236320637</v>
       </c>
       <c r="X12">
-        <v>0.08587185696398847</v>
+        <v>0.07515092266995632</v>
       </c>
       <c r="Y12">
-        <v>0.006015205223288161</v>
+        <v>4.980969325005247e-05</v>
       </c>
       <c r="Z12">
-        <v>0.1261335474739214</v>
+        <v>0.174678118503956</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.07215887094608762</v>
+        <v>0.06115630401253693</v>
       </c>
       <c r="AC12">
-        <v>-0.07215887094608762</v>
+        <v>-0.06115630401253693</v>
       </c>
       <c r="AD12">
-        <v>4591.3</v>
+        <v>5441.2</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>4591.3</v>
+        <v>5441.2</v>
       </c>
       <c r="AG12">
-        <v>2508.5</v>
+        <v>2233.5</v>
       </c>
       <c r="AH12">
-        <v>0.3976563108982409</v>
+        <v>0.4617055579126008</v>
       </c>
       <c r="AI12">
-        <v>0.4112299369446833</v>
+        <v>0.4918332113060535</v>
       </c>
       <c r="AJ12">
-        <v>0.2650822669104205</v>
+        <v>0.2603966283096079</v>
       </c>
       <c r="AK12">
-        <v>0.2762056815679366</v>
+        <v>0.2843267051964254</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1945,7 +1960,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>First Financial Holding Co., Ltd. (TWSE:2892)</t>
+          <t>The Shanghai Commercial &amp; Savings Bank, Ltd. (TWSE:5876)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1954,10 +1969,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0561</v>
+        <v>0.0436</v>
       </c>
       <c r="E13">
-        <v>0.00907</v>
+        <v>0.0462</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1972,28 +1987,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>618</v>
+        <v>516.8</v>
       </c>
       <c r="L13">
-        <v>0.3172647466502387</v>
+        <v>0.3769786271792253</v>
       </c>
       <c r="M13">
-        <v>407.8</v>
+        <v>21.3</v>
       </c>
       <c r="N13">
-        <v>0.03575123174302597</v>
+        <v>0.002874998312794418</v>
       </c>
       <c r="O13">
-        <v>0.6598705501618123</v>
+        <v>0.04121517027863777</v>
       </c>
       <c r="P13">
-        <v>407.8</v>
+        <v>21.3</v>
       </c>
       <c r="Q13">
-        <v>0.03575123174302597</v>
+        <v>0.002874998312794418</v>
       </c>
       <c r="R13">
-        <v>0.6598705501618123</v>
+        <v>0.04121517027863777</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2002,55 +2017,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1350.6</v>
+        <v>1460.3</v>
       </c>
       <c r="V13">
-        <v>0.1184051338698648</v>
+        <v>0.1971061049846802</v>
       </c>
       <c r="W13">
-        <v>0.07712852257694132</v>
+        <v>0.107331256490135</v>
       </c>
       <c r="X13">
-        <v>0.08373128810297115</v>
+        <v>0.07032037237638175</v>
       </c>
       <c r="Y13">
-        <v>-0.006602765526029827</v>
+        <v>0.03701088411375324</v>
       </c>
       <c r="Z13">
-        <v>0.09142537982436789</v>
+        <v>0.1872691408213669</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.07249903310670619</v>
+        <v>0.06177288753711747</v>
       </c>
       <c r="AC13">
-        <v>-0.07249903310670619</v>
+        <v>-0.06177288753711747</v>
       </c>
       <c r="AD13">
-        <v>6539.6</v>
+        <v>4279.5</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>6539.6</v>
+        <v>4279.5</v>
       </c>
       <c r="AG13">
-        <v>5189</v>
+        <v>2819.2</v>
       </c>
       <c r="AH13">
-        <v>0.3644002630083249</v>
+        <v>0.3661384986567649</v>
       </c>
       <c r="AI13">
-        <v>0.4887995276143778</v>
+        <v>0.3601363292097955</v>
       </c>
       <c r="AJ13">
-        <v>0.3126732386897732</v>
+        <v>0.275638205301186</v>
       </c>
       <c r="AK13">
-        <v>0.4313992833567504</v>
+        <v>0.2704865341993917</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2076,10 +2091,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0493</v>
+        <v>0.0733</v>
       </c>
       <c r="E14">
-        <v>0.0706</v>
+        <v>0.124</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2094,28 +2109,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>260.9</v>
+        <v>354.3</v>
       </c>
       <c r="L14">
-        <v>0.3453799311622981</v>
+        <v>0.3940607273940607</v>
       </c>
       <c r="M14">
-        <v>23.6</v>
+        <v>24.1</v>
       </c>
       <c r="N14">
-        <v>0.006972346962892933</v>
+        <v>0.006554790981042784</v>
       </c>
       <c r="O14">
-        <v>0.09045611345343045</v>
+        <v>0.06802145074795371</v>
       </c>
       <c r="P14">
-        <v>23.6</v>
+        <v>24.1</v>
       </c>
       <c r="Q14">
-        <v>0.006972346962892933</v>
+        <v>0.006554790981042784</v>
       </c>
       <c r="R14">
-        <v>0.09045611345343045</v>
+        <v>0.06802145074795371</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2124,55 +2139,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>807.3</v>
+        <v>1263.4</v>
       </c>
       <c r="V14">
-        <v>0.2385074450484519</v>
+        <v>0.343623357902467</v>
       </c>
       <c r="W14">
-        <v>0.07171917092748363</v>
+        <v>0.11319127184435</v>
       </c>
       <c r="X14">
-        <v>0.09560802211005445</v>
+        <v>0.07774831311653563</v>
       </c>
       <c r="Y14">
-        <v>-0.02388885118257082</v>
+        <v>0.0354429587278144</v>
       </c>
       <c r="Z14">
-        <v>0.09942875194145366</v>
+        <v>0.1525268461499313</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.07290302456882269</v>
+        <v>0.0622981049937998</v>
       </c>
       <c r="AC14">
-        <v>-0.07290302456882269</v>
+        <v>-0.0622981049937998</v>
       </c>
       <c r="AD14">
-        <v>3571.9</v>
+        <v>3707.3</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>3571.9</v>
+        <v>3707.3</v>
       </c>
       <c r="AG14">
-        <v>2764.6</v>
+        <v>2443.9</v>
       </c>
       <c r="AH14">
-        <v>0.5134474679086348</v>
+        <v>0.5020720476706393</v>
       </c>
       <c r="AI14">
-        <v>0.5329603103551179</v>
+        <v>0.5087204116638079</v>
       </c>
       <c r="AJ14">
-        <v>0.4495723159983088</v>
+        <v>0.399290919190929</v>
       </c>
       <c r="AK14">
-        <v>0.468997574091981</v>
+        <v>0.405687156587706</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2198,10 +2213,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0398</v>
+        <v>0.0613</v>
       </c>
       <c r="E15">
-        <v>0.0547</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2216,28 +2231,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>612.3</v>
+        <v>619.9</v>
       </c>
       <c r="L15">
-        <v>0.3769855929072774</v>
+        <v>0.3546541564162709</v>
       </c>
       <c r="M15">
-        <v>427.8</v>
+        <v>217.7</v>
       </c>
       <c r="N15">
-        <v>0.03608269161022596</v>
+        <v>0.01698300139639745</v>
       </c>
       <c r="O15">
-        <v>0.6986771190592848</v>
+        <v>0.3511856751088885</v>
       </c>
       <c r="P15">
-        <v>427.8</v>
+        <v>217.7</v>
       </c>
       <c r="Q15">
-        <v>0.03608269161022596</v>
+        <v>0.01698300139639745</v>
       </c>
       <c r="R15">
-        <v>0.6986771190592848</v>
+        <v>0.3511856751088885</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2246,55 +2261,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>2514.7</v>
+        <v>2164.9</v>
       </c>
       <c r="V15">
-        <v>0.212101787265627</v>
+        <v>0.1688860804917815</v>
       </c>
       <c r="W15">
-        <v>0.07283562914852615</v>
+        <v>0.09770359512664113</v>
       </c>
       <c r="X15">
-        <v>0.08834278774147364</v>
+        <v>0.07355465022183547</v>
       </c>
       <c r="Y15">
-        <v>-0.01550715859294749</v>
+        <v>0.02414894490480567</v>
       </c>
       <c r="Z15">
-        <v>0.08735686586671114</v>
+        <v>0.1371299906639574</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.07303594263244953</v>
+        <v>0.06249603800958611</v>
       </c>
       <c r="AC15">
-        <v>-0.07303594263244953</v>
+        <v>-0.06249603800958611</v>
       </c>
       <c r="AD15">
-        <v>9016</v>
+        <v>9808.4</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>9016</v>
+        <v>9808.4</v>
       </c>
       <c r="AG15">
-        <v>6501.3</v>
+        <v>7643.5</v>
       </c>
       <c r="AH15">
-        <v>0.4319642010147518</v>
+        <v>0.4334802073619686</v>
       </c>
       <c r="AI15">
-        <v>0.5810139389213608</v>
+        <v>0.5736107699685369</v>
       </c>
       <c r="AJ15">
-        <v>0.3541514593569896</v>
+        <v>0.3735424343423483</v>
       </c>
       <c r="AK15">
-        <v>0.4999846189340921</v>
+        <v>0.5118015333623489</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2320,13 +2335,13 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.0533</v>
+        <v>0.0613</v>
       </c>
       <c r="E16">
-        <v>0.0312</v>
+        <v>0.0388</v>
       </c>
       <c r="F16">
-        <v>-0.0408</v>
+        <v>0.134</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2341,28 +2356,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>513.4</v>
+        <v>621.3</v>
       </c>
       <c r="L16">
-        <v>0.312819887886912</v>
+        <v>0.32562893081761</v>
       </c>
       <c r="M16">
-        <v>281.5</v>
+        <v>88.7</v>
       </c>
       <c r="N16">
-        <v>0.02518948037189158</v>
+        <v>0.006724587578845222</v>
       </c>
       <c r="O16">
-        <v>0.5483054148811843</v>
+        <v>0.1427651698052471</v>
       </c>
       <c r="P16">
-        <v>281.5</v>
+        <v>88.7</v>
       </c>
       <c r="Q16">
-        <v>0.02518948037189158</v>
+        <v>0.006724587578845222</v>
       </c>
       <c r="R16">
-        <v>0.5483054148811843</v>
+        <v>0.1427651698052471</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2371,55 +2386,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>2954.2</v>
+        <v>1715.3</v>
       </c>
       <c r="V16">
-        <v>0.2643508451674675</v>
+        <v>0.130041545366327</v>
       </c>
       <c r="W16">
-        <v>0.07541349628367461</v>
+        <v>0.106514657980456</v>
       </c>
       <c r="X16">
-        <v>0.09457839276752869</v>
+        <v>0.07391655402821035</v>
       </c>
       <c r="Y16">
-        <v>-0.01916489648385408</v>
+        <v>0.03259810395224567</v>
       </c>
       <c r="Z16">
-        <v>0.1187038912194416</v>
+        <v>0.1356742112336541</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.07360323046718929</v>
+        <v>0.062528862050096</v>
       </c>
       <c r="AC16">
-        <v>-0.07360323046718929</v>
+        <v>-0.062528862050096</v>
       </c>
       <c r="AD16">
-        <v>11326.1</v>
+        <v>10369.6</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>11326.1</v>
+        <v>10369.6</v>
       </c>
       <c r="AG16">
-        <v>8371.900000000001</v>
+        <v>8654.300000000001</v>
       </c>
       <c r="AH16">
-        <v>0.5033509026105042</v>
+        <v>0.4401358234295416</v>
       </c>
       <c r="AI16">
-        <v>0.6598791649916393</v>
+        <v>0.5933521397549825</v>
       </c>
       <c r="AJ16">
-        <v>0.4282915200130966</v>
+        <v>0.3961739003053373</v>
       </c>
       <c r="AK16">
-        <v>0.5891679627296847</v>
+        <v>0.5490958695514244</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2436,7 +2451,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SinoPac Financial Holdings Company Limited (TWSE:2890)</t>
+          <t>First Financial Holding Co., Ltd. (TWSE:2892)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2445,10 +2460,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.09140000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="E17">
-        <v>0.15</v>
+        <v>0.09179999999999999</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2463,28 +2478,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>514.4</v>
+        <v>720.8</v>
       </c>
       <c r="L17">
-        <v>0.3633281536940246</v>
+        <v>0.3797881869434638</v>
       </c>
       <c r="M17">
-        <v>283.6</v>
+        <v>328.7</v>
       </c>
       <c r="N17">
-        <v>0.04565210392453559</v>
+        <v>0.02698553437433296</v>
       </c>
       <c r="O17">
-        <v>0.5513219284603422</v>
+        <v>0.4560210876803552</v>
       </c>
       <c r="P17">
-        <v>283.6</v>
+        <v>328.7</v>
       </c>
       <c r="Q17">
-        <v>0.04565210392453559</v>
+        <v>0.02698553437433296</v>
       </c>
       <c r="R17">
-        <v>0.5513219284603422</v>
+        <v>0.4560210876803552</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2493,55 +2508,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>2247.1</v>
+        <v>1828.6</v>
       </c>
       <c r="V17">
-        <v>0.3617237049676443</v>
+        <v>0.1501239676206426</v>
       </c>
       <c r="W17">
-        <v>0.08969798423659063</v>
+        <v>0.1053909025777492</v>
       </c>
       <c r="X17">
-        <v>0.1162703772380075</v>
+        <v>0.08213142226910891</v>
       </c>
       <c r="Y17">
-        <v>-0.02657239300141689</v>
+        <v>0.02325948030864027</v>
       </c>
       <c r="Z17">
-        <v>0.1078745856985028</v>
+        <v>0.1577862208292111</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.07480379725299188</v>
+        <v>0.06311016461286</v>
       </c>
       <c r="AC17">
-        <v>-0.07480379725299188</v>
+        <v>-0.06311016461286</v>
       </c>
       <c r="AD17">
-        <v>11764.4</v>
+        <v>15377.6</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>11764.4</v>
+        <v>15377.6</v>
       </c>
       <c r="AG17">
-        <v>9517.299999999999</v>
+        <v>13549</v>
       </c>
       <c r="AH17">
-        <v>0.6544285348731128</v>
+        <v>0.5580045140829227</v>
       </c>
       <c r="AI17">
-        <v>0.7168781153644596</v>
+        <v>0.6715666365331622</v>
       </c>
       <c r="AJ17">
-        <v>0.6050605550081057</v>
+        <v>0.5265919407997015</v>
       </c>
       <c r="AK17">
-        <v>0.6719596145020651</v>
+        <v>0.6430622463750919</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2558,7 +2573,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Taishin Financial Holding Co., Ltd. (TWSE:2887)</t>
+          <t>SinoPac Financial Holdings Company Limited (TWSE:2890)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2567,10 +2582,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.0483</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="E18">
-        <v>-0.0214</v>
+        <v>0.13</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2585,28 +2600,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>338.8</v>
+        <v>582.3</v>
       </c>
       <c r="L18">
-        <v>0.2498156614068721</v>
+        <v>0.3798682236284167</v>
       </c>
       <c r="M18">
-        <v>272.4</v>
+        <v>226.2</v>
       </c>
       <c r="N18">
-        <v>0.04628323846741993</v>
+        <v>0.028401742777143</v>
       </c>
       <c r="O18">
-        <v>0.8040141676505312</v>
+        <v>0.3884595569294179</v>
       </c>
       <c r="P18">
-        <v>272.4</v>
+        <v>226.2</v>
       </c>
       <c r="Q18">
-        <v>0.04628323846741993</v>
+        <v>0.028401742777143</v>
       </c>
       <c r="R18">
-        <v>0.8040141676505312</v>
+        <v>0.3884595569294179</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2615,55 +2630,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>1658.3</v>
+        <v>988.3</v>
       </c>
       <c r="V18">
-        <v>0.2817602582618299</v>
+        <v>0.124091257235413</v>
       </c>
       <c r="W18">
-        <v>0.0504895459219409</v>
+        <v>0.1253282252163058</v>
       </c>
       <c r="X18">
-        <v>0.1233786127558041</v>
+        <v>0.08568051616746755</v>
       </c>
       <c r="Y18">
-        <v>-0.0728890668338632</v>
+        <v>0.03964770904883824</v>
       </c>
       <c r="Z18">
-        <v>0.08312188185685042</v>
+        <v>0.109224476999373</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.07505272327048165</v>
+        <v>0.06329190311096147</v>
       </c>
       <c r="AC18">
-        <v>-0.07505272327048165</v>
+        <v>-0.06329190311096147</v>
       </c>
       <c r="AD18">
-        <v>12843.4</v>
+        <v>11693.6</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>12843.4</v>
+        <v>11693.6</v>
       </c>
       <c r="AG18">
-        <v>11185.1</v>
+        <v>10705.3</v>
       </c>
       <c r="AH18">
-        <v>0.6857530340810191</v>
+        <v>0.594854994684071</v>
       </c>
       <c r="AI18">
-        <v>0.6783927826284459</v>
+        <v>0.6786018953220481</v>
       </c>
       <c r="AJ18">
-        <v>0.6552259440207141</v>
+        <v>0.5734081072974246</v>
       </c>
       <c r="AK18">
-        <v>0.6475182067640011</v>
+        <v>0.6590472555344874</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2680,7 +2695,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CTBC Financial Holding Co., Ltd. (TWSE:2891)</t>
+          <t>Taishin Financial Holding Co., Ltd. (TWSE:2887)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2689,124 +2704,109 @@
         </is>
       </c>
       <c r="D19">
-        <v>-0.08699999999999999</v>
+        <v>0.0727</v>
       </c>
       <c r="E19">
-        <v>0.0231</v>
-      </c>
-      <c r="F19">
-        <v>-0.00315</v>
+        <v>0.0607</v>
       </c>
       <c r="G19">
-        <v>0.4054979615608619</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0.4054979615608619</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>-0.007326732673267326</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>-0.005359303168237383</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>1255.7</v>
+        <v>580.9</v>
       </c>
       <c r="L19">
-        <v>0.146266744321491</v>
+        <v>0.3506791427709025</v>
       </c>
       <c r="M19">
-        <v>783.2799</v>
+        <v>353.8</v>
       </c>
       <c r="N19">
-        <v>0.05421372508305648</v>
+        <v>0.04410976324352629</v>
       </c>
       <c r="O19">
-        <v>0.6237794855459107</v>
+        <v>0.6090549147873989</v>
       </c>
       <c r="P19">
-        <v>783.2799</v>
+        <v>189.8</v>
       </c>
       <c r="Q19">
-        <v>0.05421372508305648</v>
+        <v>0.02366317994240048</v>
       </c>
       <c r="R19">
-        <v>0.6237794855459107</v>
+        <v>0.3267343776897917</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>0.4635387224420576</v>
       </c>
       <c r="U19">
-        <v>14998.5</v>
+        <v>1517.1</v>
       </c>
       <c r="V19">
-        <v>1.038102159468439</v>
+        <v>0.1891433629642559</v>
       </c>
       <c r="W19">
-        <v>0.08533991205714248</v>
+        <v>0.1011686027273202</v>
       </c>
       <c r="X19">
-        <v>0.09329362408039482</v>
+        <v>0.08604066865001087</v>
       </c>
       <c r="Y19">
-        <v>-0.007953712023252346</v>
+        <v>0.01512793407730936</v>
       </c>
       <c r="Z19">
-        <v>0.8175723292002363</v>
+        <v>0.09618008581597756</v>
       </c>
       <c r="AA19">
-        <v>-0.004381617974146043</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.07349832038118259</v>
+        <v>0.06330866602955332</v>
       </c>
       <c r="AC19">
-        <v>-0.07787993835532864</v>
+        <v>-0.06330866602955332</v>
       </c>
       <c r="AD19">
-        <v>13889.7</v>
+        <v>11944.2</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>13889.7</v>
+        <v>11944.2</v>
       </c>
       <c r="AG19">
-        <v>-1108.799999999999</v>
+        <v>10427.1</v>
       </c>
       <c r="AH19">
-        <v>0.4901491652462974</v>
+        <v>0.5982539531482438</v>
       </c>
       <c r="AI19">
-        <v>0.5569201530059903</v>
+        <v>0.6470769880869184</v>
       </c>
       <c r="AJ19">
-        <v>-0.08312342569269515</v>
+        <v>0.5652157415437988</v>
       </c>
       <c r="AK19">
-        <v>-0.1115302211895349</v>
+        <v>0.6154731548377957</v>
       </c>
       <c r="AL19">
-        <v>703.7</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>703.7</v>
-      </c>
-      <c r="AN19">
-        <v>1521.325301204819</v>
-      </c>
-      <c r="AO19">
-        <v>-0.08938468097200511</v>
-      </c>
-      <c r="AP19">
-        <v>-121.44578313253</v>
-      </c>
-      <c r="AQ19">
-        <v>-0.08938468097200511</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/taiwan/taiwan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0613</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0607</v>
+        <v>0.06795</v>
       </c>
       <c r="F2">
-        <v>0.143</v>
+        <v>0.06235</v>
       </c>
       <c r="G2">
-        <v>0.02195164483469591</v>
+        <v>0.1647696163616763</v>
       </c>
       <c r="H2">
-        <v>0.02195164483469591</v>
+        <v>0.1647696163616763</v>
       </c>
       <c r="I2">
-        <v>0.124489558046626</v>
+        <v>0.2115518435809536</v>
       </c>
       <c r="J2">
-        <v>0.1058873947787764</v>
+        <v>0.1732559904825418</v>
       </c>
       <c r="K2">
-        <v>8328.809999999999</v>
+        <v>6861.099999999999</v>
       </c>
       <c r="L2">
-        <v>0.2847836121739309</v>
+        <v>0.2333286856451048</v>
       </c>
       <c r="M2">
-        <v>3049.8723</v>
+        <v>3462.4</v>
       </c>
       <c r="N2">
-        <v>0.02390828476351365</v>
+        <v>0.0371531246546135</v>
       </c>
       <c r="O2">
-        <v>0.3661834403714336</v>
+        <v>0.5046421127807494</v>
       </c>
       <c r="P2">
-        <v>2882.7823</v>
+        <v>3462.4</v>
       </c>
       <c r="Q2">
-        <v>0.02259844785619936</v>
+        <v>0.0371531246546135</v>
       </c>
       <c r="R2">
-        <v>0.3461217508863811</v>
+        <v>0.5046421127807494</v>
       </c>
       <c r="S2">
-        <v>167.09</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.0547859003801569</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>35206.3</v>
+        <v>21160.5</v>
       </c>
       <c r="V2">
-        <v>0.2759860620622347</v>
+        <v>0.2270617762979289</v>
       </c>
       <c r="W2">
-        <v>0.106514657980456</v>
+        <v>0.09752392891198172</v>
       </c>
       <c r="X2">
-        <v>0.07774831311653563</v>
+        <v>0.08098469052821072</v>
       </c>
       <c r="Y2">
-        <v>0.02876634486392039</v>
+        <v>0.016539238383771</v>
       </c>
       <c r="Z2">
-        <v>0.1769280365625745</v>
+        <v>0.2331870836908492</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06177288753711747</v>
+        <v>0.06655326317559815</v>
       </c>
       <c r="AC2">
-        <v>-0.0601211766328185</v>
+        <v>-0.06628233193915622</v>
       </c>
       <c r="AD2">
-        <v>138670.9</v>
+        <v>98156.60000000001</v>
       </c>
       <c r="AE2">
-        <v>109.3296820628648</v>
+        <v>110.2728697449233</v>
       </c>
       <c r="AF2">
-        <v>138780.2296820629</v>
+        <v>98266.87286974493</v>
       </c>
       <c r="AG2">
-        <v>103573.9296820629</v>
+        <v>77106.37286974493</v>
       </c>
       <c r="AH2">
-        <v>0.5210529556742846</v>
+        <v>0.513251290582365</v>
       </c>
       <c r="AI2">
-        <v>0.6047249862090748</v>
+        <v>0.5673774935800133</v>
       </c>
       <c r="AJ2">
-        <v>0.4481015196088827</v>
+        <v>0.4527703619897013</v>
       </c>
       <c r="AK2">
-        <v>0.5330980481361219</v>
+        <v>0.5071640801636721</v>
       </c>
       <c r="AL2">
-        <v>2394.1</v>
+        <v>3408.9</v>
       </c>
       <c r="AM2">
-        <v>2394.1</v>
+        <v>3408.9</v>
       </c>
       <c r="AN2">
-        <v>36.84332323715394</v>
+        <v>15.45919299461366</v>
       </c>
       <c r="AO2">
-        <v>1.504197819639948</v>
+        <v>1.813341547126639</v>
       </c>
       <c r="AP2">
-        <v>27.51844669803466</v>
+        <v>12.143883338543</v>
       </c>
       <c r="AQ2">
-        <v>1.504197819639948</v>
+        <v>1.813341547126639</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0309</v>
+        <v>0.0261</v>
       </c>
       <c r="E3">
-        <v>0.0495</v>
+        <v>0.0901</v>
       </c>
       <c r="F3">
-        <v>0.31</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="G3">
-        <v>0.05703472721942379</v>
+        <v>0.3053589548052865</v>
       </c>
       <c r="H3">
-        <v>0.05703472721942379</v>
+        <v>0.3053589548052865</v>
       </c>
       <c r="I3">
-        <v>0.3199275072625996</v>
+        <v>0.3895846069490575</v>
       </c>
       <c r="J3">
-        <v>0.2781095256421736</v>
+        <v>0.3210098426710831</v>
       </c>
       <c r="K3">
-        <v>1481.6</v>
+        <v>2082.6</v>
       </c>
       <c r="L3">
-        <v>0.1316240682995301</v>
+        <v>0.1312543723096509</v>
       </c>
       <c r="M3">
-        <v>622.5822999999999</v>
+        <v>1112</v>
       </c>
       <c r="N3">
-        <v>0.03350206636030004</v>
+        <v>0.04751507278950225</v>
       </c>
       <c r="O3">
-        <v>0.4202094357451404</v>
+        <v>0.5339479496782867</v>
       </c>
       <c r="P3">
-        <v>622.5822999999999</v>
+        <v>1112</v>
       </c>
       <c r="Q3">
-        <v>0.03350206636030004</v>
+        <v>0.04751507278950225</v>
       </c>
       <c r="R3">
-        <v>0.4202094357451404</v>
+        <v>0.5339479496782867</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14484.7</v>
+        <v>4173.2</v>
       </c>
       <c r="V3">
-        <v>0.779442943702444</v>
+        <v>0.1783182569830493</v>
       </c>
       <c r="W3">
-        <v>0.1450614866452573</v>
+        <v>0.1640359168241966</v>
       </c>
       <c r="X3">
-        <v>0.07587959904606612</v>
+        <v>0.07843480419395102</v>
       </c>
       <c r="Y3">
-        <v>0.06918188759919117</v>
+        <v>0.08560111263024558</v>
       </c>
       <c r="Z3">
-        <v>1.294512040849185</v>
+        <v>1.09190442765322</v>
       </c>
       <c r="AA3">
-        <v>0.3600161296186489</v>
+        <v>0.3505120685328191</v>
       </c>
       <c r="AB3">
-        <v>0.06269427417774805</v>
+        <v>0.06650369121266977</v>
       </c>
       <c r="AC3">
-        <v>0.2973218554409009</v>
+        <v>0.2840083773201493</v>
       </c>
       <c r="AD3">
-        <v>16724.5</v>
+        <v>17997.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>16724.5</v>
+        <v>17997.8</v>
       </c>
       <c r="AG3">
-        <v>2239.799999999999</v>
+        <v>13824.6</v>
       </c>
       <c r="AH3">
-        <v>0.4736758629088674</v>
+        <v>0.4347200181638564</v>
       </c>
       <c r="AI3">
-        <v>0.5522589635382614</v>
+        <v>0.5282594658056942</v>
       </c>
       <c r="AJ3">
-        <v>0.1075627185062814</v>
+        <v>0.3713525143911657</v>
       </c>
       <c r="AK3">
-        <v>0.1417675690387427</v>
+        <v>0.4624106927831741</v>
       </c>
       <c r="AL3">
-        <v>2394.1</v>
+        <v>3408.9</v>
       </c>
       <c r="AM3">
-        <v>2394.1</v>
+        <v>3408.9</v>
       </c>
       <c r="AN3">
-        <v>4.517327066958377</v>
+        <v>2.862200028625498</v>
       </c>
       <c r="AO3">
-        <v>1.504197819639948</v>
+        <v>1.813341547126639</v>
       </c>
       <c r="AP3">
-        <v>0.6049752856332548</v>
+        <v>2.198533738331133</v>
       </c>
       <c r="AQ3">
-        <v>1.504197819639948</v>
+        <v>1.813341547126639</v>
       </c>
     </row>
     <row r="4">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0678</v>
+        <v>0.076</v>
       </c>
       <c r="E4">
-        <v>0.0935</v>
+        <v>0.101</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -874,34 +874,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.07303125776198093</v>
+        <v>0.06601417334064816</v>
       </c>
       <c r="J4">
-        <v>0.06066403868330568</v>
+        <v>0.05599576221036009</v>
       </c>
       <c r="K4">
-        <v>150</v>
+        <v>156.2</v>
       </c>
       <c r="L4">
-        <v>0.2763957987838584</v>
+        <v>0.2627417998317914</v>
       </c>
       <c r="M4">
-        <v>11.4</v>
+        <v>24.8</v>
       </c>
       <c r="N4">
-        <v>0.006418557513653511</v>
+        <v>0.01316208470438382</v>
       </c>
       <c r="O4">
-        <v>0.076</v>
+        <v>0.1587708066581306</v>
       </c>
       <c r="P4">
-        <v>11.4</v>
+        <v>24.8</v>
       </c>
       <c r="Q4">
-        <v>0.006418557513653511</v>
+        <v>0.01316208470438382</v>
       </c>
       <c r="R4">
-        <v>0.076</v>
+        <v>0.1587708066581306</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -910,55 +910,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>330.5</v>
+        <v>268.9</v>
       </c>
       <c r="V4">
-        <v>0.1860818647598671</v>
+        <v>0.1427130877826133</v>
       </c>
       <c r="W4">
-        <v>0.08409957389549226</v>
+        <v>0.07878543326944416</v>
       </c>
       <c r="X4">
-        <v>0.09060626201415681</v>
+        <v>0.092889172221505</v>
       </c>
       <c r="Y4">
-        <v>-0.006506688118664547</v>
+        <v>-0.01410373895206084</v>
       </c>
       <c r="Z4">
-        <v>0.1283091052395196</v>
+        <v>0.1246704236757948</v>
       </c>
       <c r="AA4">
-        <v>0.007783748523670558</v>
+        <v>0.00698101539881465</v>
       </c>
       <c r="AB4">
-        <v>0.06349912796742367</v>
+        <v>0.06672166322969861</v>
       </c>
       <c r="AC4">
-        <v>-0.05571537944375311</v>
+        <v>-0.05974064783088396</v>
       </c>
       <c r="AD4">
-        <v>3005.7</v>
+        <v>3023.7</v>
       </c>
       <c r="AE4">
-        <v>109.3296820628648</v>
+        <v>110.2728697449233</v>
       </c>
       <c r="AF4">
-        <v>3115.029682062865</v>
+        <v>3133.972869744923</v>
       </c>
       <c r="AG4">
-        <v>2784.529682062865</v>
+        <v>2865.072869744923</v>
       </c>
       <c r="AH4">
-        <v>0.6368732551677266</v>
+        <v>0.6245246927701446</v>
       </c>
       <c r="AI4">
-        <v>0.5957868559941762</v>
+        <v>0.5625135748432517</v>
       </c>
       <c r="AJ4">
-        <v>0.6105581632761214</v>
+        <v>0.6032655836637162</v>
       </c>
       <c r="AK4">
-        <v>0.5685115677059093</v>
+        <v>0.540327681088682</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -967,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>48.87317073170731</v>
+        <v>49.32626427406199</v>
       </c>
       <c r="AP4">
-        <v>45.27690539939617</v>
+        <v>46.73854599910152</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>O-Bank Co., Ltd. (TWSE:2897)</t>
+          <t>Chang Hwa Commercial Bank, Ltd. (TWSE:2801)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.109</v>
+        <v>0.0417</v>
       </c>
       <c r="E5">
-        <v>0.487</v>
+        <v>0.0372</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1008,85 +1008,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>170.1</v>
+        <v>440.6</v>
       </c>
       <c r="L5">
-        <v>0.4545697487974345</v>
+        <v>0.3742779476724431</v>
       </c>
       <c r="M5">
-        <v>35.39</v>
+        <v>188</v>
       </c>
       <c r="N5">
-        <v>0.03999321957283309</v>
+        <v>0.03081007555023845</v>
       </c>
       <c r="O5">
-        <v>0.2080540858318636</v>
+        <v>0.4266908760780753</v>
       </c>
       <c r="P5">
-        <v>32.3</v>
+        <v>188</v>
       </c>
       <c r="Q5">
-        <v>0.03650129958187365</v>
+        <v>0.03081007555023845</v>
       </c>
       <c r="R5">
-        <v>0.1898883009994121</v>
+        <v>0.4266908760780753</v>
       </c>
       <c r="S5">
-        <v>3.090000000000003</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.08731280022605266</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>590.5</v>
+        <v>4300</v>
       </c>
       <c r="V5">
-        <v>0.6673070403435417</v>
+        <v>0.7046985365214115</v>
       </c>
       <c r="W5">
-        <v>0.1729713239780354</v>
+        <v>0.0783720806133158</v>
       </c>
       <c r="X5">
-        <v>0.2038366256865331</v>
+        <v>0.08084487890226502</v>
       </c>
       <c r="Y5">
-        <v>-0.03086530170849774</v>
+        <v>-0.002472798288949224</v>
       </c>
       <c r="Z5">
-        <v>0.04768033027102101</v>
+        <v>0.1498586959289152</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05870402742080873</v>
+        <v>0.06521390117528393</v>
       </c>
       <c r="AC5">
-        <v>-0.05870402742080873</v>
+        <v>-0.06521390117528393</v>
       </c>
       <c r="AD5">
-        <v>7361.7</v>
+        <v>5602.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>7361.7</v>
+        <v>5602.4</v>
       </c>
       <c r="AG5">
-        <v>6771.2</v>
+        <v>1302.4</v>
       </c>
       <c r="AH5">
-        <v>0.8926951713433414</v>
+        <v>0.4786616884392915</v>
       </c>
       <c r="AI5">
-        <v>0.806867752471558</v>
+        <v>0.4710392897079966</v>
       </c>
       <c r="AJ5">
-        <v>0.8844189600449315</v>
+        <v>0.1758977891225369</v>
       </c>
       <c r="AK5">
-        <v>0.7935030996214829</v>
+        <v>0.1715105943084398</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hua Nan Financial Holdings Co., Ltd. (TWSE:2880)</t>
+          <t>The Shanghai Commercial &amp; Savings Bank, Ltd. (TWSE:5876)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0626</v>
+        <v>-0.0418</v>
       </c>
       <c r="E6">
-        <v>0.0766</v>
+        <v>-0.0659</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1130,28 +1130,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>631</v>
+        <v>331.5</v>
       </c>
       <c r="L6">
-        <v>0.3676299230948497</v>
+        <v>0.3249044398706263</v>
       </c>
       <c r="M6">
-        <v>249.3</v>
+        <v>275.2</v>
       </c>
       <c r="N6">
-        <v>0.02504998944946293</v>
+        <v>0.04696806785793525</v>
       </c>
       <c r="O6">
-        <v>0.3950871632329636</v>
+        <v>0.8301659125188536</v>
       </c>
       <c r="P6">
-        <v>249.3</v>
+        <v>275.2</v>
       </c>
       <c r="Q6">
-        <v>0.02504998944946293</v>
+        <v>0.04696806785793525</v>
       </c>
       <c r="R6">
-        <v>0.3950871632329636</v>
+        <v>0.8301659125188536</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1160,55 +1160,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1231.9</v>
+        <v>1303.4</v>
       </c>
       <c r="V6">
-        <v>0.1237829201876991</v>
+        <v>0.2224497806905262</v>
       </c>
       <c r="W6">
-        <v>0.1128034609746505</v>
+        <v>0.05874638926792961</v>
       </c>
       <c r="X6">
-        <v>0.08728975532582872</v>
+        <v>0.07547120500680471</v>
       </c>
       <c r="Y6">
-        <v>0.02551370564882179</v>
+        <v>-0.0167248157388751</v>
       </c>
       <c r="Z6">
-        <v>0.1007210793656755</v>
+        <v>0.1206159535079465</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05922858431405595</v>
+        <v>0.06601494838198529</v>
       </c>
       <c r="AC6">
-        <v>-0.05922858431405595</v>
+        <v>-0.06601494838198529</v>
       </c>
       <c r="AD6">
-        <v>15540.8</v>
+        <v>3431.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>15540.8</v>
+        <v>3431.7</v>
       </c>
       <c r="AG6">
-        <v>14308.9</v>
+        <v>2128.3</v>
       </c>
       <c r="AH6">
-        <v>0.6096128726037445</v>
+        <v>0.3693574426864707</v>
       </c>
       <c r="AI6">
-        <v>0.7187593944971951</v>
+        <v>0.2956374162201278</v>
       </c>
       <c r="AJ6">
-        <v>0.5897901982605828</v>
+        <v>0.266450498272322</v>
       </c>
       <c r="AK6">
-        <v>0.7017675504418877</v>
+        <v>0.2065428360700283</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Far Eastern International Bank Ltd. (TWSE:2845)</t>
+          <t>Taiwan Business Bank, Ltd. (TWSE:2834)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0452</v>
+        <v>0.064</v>
       </c>
       <c r="E7">
-        <v>0.08220000000000001</v>
+        <v>0.09480000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1252,28 +1252,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>143.3</v>
+        <v>348.4</v>
       </c>
       <c r="L7">
-        <v>0.3685699588477366</v>
+        <v>0.3808482728465238</v>
       </c>
       <c r="M7">
-        <v>98.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="N7">
-        <v>0.05874300678490656</v>
+        <v>0.01856399884426466</v>
       </c>
       <c r="O7">
-        <v>0.6887648290300069</v>
+        <v>0.2212973593570609</v>
       </c>
       <c r="P7">
-        <v>98.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="Q7">
-        <v>0.05874300678490656</v>
+        <v>0.01856399884426466</v>
       </c>
       <c r="R7">
-        <v>0.6887648290300069</v>
+        <v>0.2212973593570609</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1282,55 +1282,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1146</v>
+        <v>914.8</v>
       </c>
       <c r="V7">
-        <v>0.6820616593262706</v>
+        <v>0.2202638929018588</v>
       </c>
       <c r="W7">
-        <v>0.08699611461874697</v>
+        <v>0.09731299927378359</v>
       </c>
       <c r="X7">
-        <v>0.08138933038391144</v>
+        <v>0.08000961305715337</v>
       </c>
       <c r="Y7">
-        <v>0.00560678423483553</v>
+        <v>0.01730338621663022</v>
       </c>
       <c r="Z7">
-        <v>0.1294791527907286</v>
+        <v>0.1518567088859747</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.0593400940938377</v>
+        <v>0.06601764286054923</v>
       </c>
       <c r="AC7">
-        <v>-0.0593400940938377</v>
+        <v>-0.06601764286054923</v>
       </c>
       <c r="AD7">
-        <v>2048.9</v>
+        <v>3598.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2048.9</v>
+        <v>3598.6</v>
       </c>
       <c r="AG7">
-        <v>902.9000000000001</v>
+        <v>2683.8</v>
       </c>
       <c r="AH7">
-        <v>0.5494355206350058</v>
+        <v>0.4642276632524059</v>
       </c>
       <c r="AI7">
-        <v>0.5332344368103269</v>
+        <v>0.467144377807202</v>
       </c>
       <c r="AJ7">
-        <v>0.3495412488869962</v>
+        <v>0.392540587977183</v>
       </c>
       <c r="AK7">
-        <v>0.3348538792464026</v>
+        <v>0.395339245205197</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mega Financial Holding Co., Ltd. (TWSE:2886)</t>
+          <t>E.SUN Financial Holding Company, Ltd. (TWSE:2884)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1356,13 +1356,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0213</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="E8">
-        <v>0.0366</v>
+        <v>0.0649</v>
       </c>
       <c r="F8">
-        <v>0.143</v>
+        <v>0.0339</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1377,28 +1377,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>985.2</v>
+        <v>842</v>
       </c>
       <c r="L8">
-        <v>0.4913715710723192</v>
+        <v>0.3708597603946441</v>
       </c>
       <c r="M8">
-        <v>481.8</v>
+        <v>591.8</v>
       </c>
       <c r="N8">
-        <v>0.02679942151518523</v>
+        <v>0.0450014067692214</v>
       </c>
       <c r="O8">
-        <v>0.4890377588306943</v>
+        <v>0.7028503562945367</v>
       </c>
       <c r="P8">
-        <v>481.8</v>
+        <v>591.8</v>
       </c>
       <c r="Q8">
-        <v>0.02679942151518523</v>
+        <v>0.0450014067692214</v>
       </c>
       <c r="R8">
-        <v>0.4890377588306943</v>
+        <v>0.7028503562945367</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1407,55 +1407,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>2255</v>
+        <v>2041.9</v>
       </c>
       <c r="V8">
-        <v>0.1254310824340861</v>
+        <v>0.1552693012539257</v>
       </c>
       <c r="W8">
-        <v>0.106970684039088</v>
+        <v>0.1185648304607412</v>
       </c>
       <c r="X8">
-        <v>0.07801488265315049</v>
+        <v>0.080479851249158</v>
       </c>
       <c r="Y8">
-        <v>0.02895580138593747</v>
+        <v>0.03808497921158323</v>
       </c>
       <c r="Z8">
-        <v>0.0708030228123455</v>
+        <v>0.1453939995517274</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05942081272452453</v>
+        <v>0.06654702101776321</v>
       </c>
       <c r="AC8">
-        <v>-0.05942081272452453</v>
+        <v>-0.06654702101776321</v>
       </c>
       <c r="AD8">
-        <v>18405.5</v>
+        <v>11777.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>18405.5</v>
+        <v>11777.2</v>
       </c>
       <c r="AG8">
-        <v>16150.5</v>
+        <v>9735.300000000001</v>
       </c>
       <c r="AH8">
-        <v>0.5058749158272293</v>
+        <v>0.47245054737864</v>
       </c>
       <c r="AI8">
-        <v>0.6503963051567375</v>
+        <v>0.6017679219252977</v>
       </c>
       <c r="AJ8">
-        <v>0.4732261892553145</v>
+        <v>0.4253823298086167</v>
       </c>
       <c r="AK8">
-        <v>0.620126017992697</v>
+        <v>0.5553793406392799</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>King's Town Bank (TWSE:2809)</t>
+          <t>Taiwan Cooperative Financial Holding Co., Ltd. (TWSE:5880)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0394</v>
+        <v>0.0624</v>
       </c>
       <c r="E9">
-        <v>0.0239</v>
+        <v>0.0268</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1499,28 +1499,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>174.3</v>
+        <v>584.8</v>
       </c>
       <c r="L9">
-        <v>0.602280580511403</v>
+        <v>0.3188137164040779</v>
       </c>
       <c r="M9">
-        <v>38</v>
+        <v>301</v>
       </c>
       <c r="N9">
-        <v>0.02622498274672188</v>
+        <v>0.02667115616360672</v>
       </c>
       <c r="O9">
-        <v>0.2180149168100975</v>
+        <v>0.5147058823529412</v>
       </c>
       <c r="P9">
-        <v>38</v>
+        <v>301</v>
       </c>
       <c r="Q9">
-        <v>0.02622498274672188</v>
+        <v>0.02667115616360672</v>
       </c>
       <c r="R9">
-        <v>0.2180149168100975</v>
+        <v>0.5147058823529412</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1529,55 +1529,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>345.7</v>
+        <v>2112.6</v>
       </c>
       <c r="V9">
-        <v>0.2385783298826777</v>
+        <v>0.1871943007017793</v>
       </c>
       <c r="W9">
-        <v>0.1392172523961661</v>
+        <v>0.08213483146067416</v>
       </c>
       <c r="X9">
-        <v>0.07420188140590672</v>
+        <v>0.08112450215415642</v>
       </c>
       <c r="Y9">
-        <v>0.06501537099025942</v>
+        <v>0.001010329306517732</v>
       </c>
       <c r="Z9">
-        <v>0.1014797671645978</v>
+        <v>0.124982965849936</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05953310752901077</v>
+        <v>0.06655950533343309</v>
       </c>
       <c r="AC9">
-        <v>-0.05953310752901077</v>
+        <v>-0.06655950533343309</v>
       </c>
       <c r="AD9">
-        <v>1163.1</v>
+        <v>10557</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1163.1</v>
+        <v>10557</v>
       </c>
       <c r="AG9">
-        <v>817.3999999999999</v>
+        <v>8444.4</v>
       </c>
       <c r="AH9">
-        <v>0.4452739175376134</v>
+        <v>0.4833215825954786</v>
       </c>
       <c r="AI9">
-        <v>0.4464532473514509</v>
+        <v>0.5634486881151128</v>
       </c>
       <c r="AJ9">
-        <v>0.3606600776561948</v>
+        <v>0.4279979726305119</v>
       </c>
       <c r="AK9">
-        <v>0.3617614516485947</v>
+        <v>0.5079705001263249</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Taichung Commercial Bank Co., Ltd. (TWSE:2812)</t>
+          <t>SinoPac Financial Holdings Company Limited (TWSE:2890)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0649</v>
+        <v>0.122</v>
       </c>
       <c r="E10">
-        <v>0.0955</v>
+        <v>0.153</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1621,28 +1621,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>195.9</v>
+        <v>708.5</v>
       </c>
       <c r="L10">
-        <v>0.4139898562975486</v>
+        <v>0.3800761761708063</v>
       </c>
       <c r="M10">
-        <v>46.8</v>
+        <v>292.3</v>
       </c>
       <c r="N10">
-        <v>0.01725600088492312</v>
+        <v>0.03295674919947684</v>
       </c>
       <c r="O10">
-        <v>0.2388973966309341</v>
+        <v>0.4125617501764291</v>
       </c>
       <c r="P10">
-        <v>46.8</v>
+        <v>292.3</v>
       </c>
       <c r="Q10">
-        <v>0.01725600088492312</v>
+        <v>0.03295674919947684</v>
       </c>
       <c r="R10">
-        <v>0.2388973966309341</v>
+        <v>0.4125617501764291</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1651,55 +1651,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>446</v>
+        <v>1418.8</v>
       </c>
       <c r="V10">
-        <v>0.1644482135614468</v>
+        <v>0.1599693320705362</v>
       </c>
       <c r="W10">
-        <v>0.0960623743441377</v>
+        <v>0.1279273423252623</v>
       </c>
       <c r="X10">
-        <v>0.07091816173188349</v>
+        <v>0.08942242076477458</v>
       </c>
       <c r="Y10">
-        <v>0.0251442126122542</v>
+        <v>0.03850492156048768</v>
       </c>
       <c r="Z10">
-        <v>0.1794259280324574</v>
+        <v>0.1149983343409542</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.0596544961299126</v>
+        <v>0.06668389684972251</v>
       </c>
       <c r="AC10">
-        <v>-0.0596544961299126</v>
+        <v>-0.06668389684972251</v>
       </c>
       <c r="AD10">
-        <v>1660.6</v>
+        <v>12849.8</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1660.6</v>
+        <v>12849.8</v>
       </c>
       <c r="AG10">
-        <v>1214.6</v>
+        <v>11431</v>
       </c>
       <c r="AH10">
-        <v>0.3797653623619274</v>
+        <v>0.5916386573967494</v>
       </c>
       <c r="AI10">
-        <v>0.4216433069266707</v>
+        <v>0.6670889033095392</v>
       </c>
       <c r="AJ10">
-        <v>0.3093182570606361</v>
+        <v>0.5630979005132954</v>
       </c>
       <c r="AK10">
-        <v>0.3477837590195854</v>
+        <v>0.6406182574241889</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EnTie Commercial Bank Co., Ltd. (TWSE:2849)</t>
+          <t>First Financial Holding Co., Ltd. (TWSE:2892)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.09619999999999999</v>
+        <v>0.0252</v>
       </c>
       <c r="E11">
-        <v>-0.353</v>
+        <v>0.0571</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1743,28 +1743,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>6.81</v>
+        <v>763.3</v>
       </c>
       <c r="L11">
-        <v>0.06618075801749271</v>
+        <v>0.3770313657693257</v>
       </c>
       <c r="M11">
-        <v>24.3</v>
+        <v>364.5</v>
       </c>
       <c r="N11">
-        <v>0.02569796954314721</v>
+        <v>0.03142864533485087</v>
       </c>
       <c r="O11">
-        <v>3.568281938325991</v>
+        <v>0.4775317699462859</v>
       </c>
       <c r="P11">
-        <v>24.3</v>
+        <v>364.5</v>
       </c>
       <c r="Q11">
-        <v>0.02569796954314721</v>
+        <v>0.03142864533485087</v>
       </c>
       <c r="R11">
-        <v>3.568281938325991</v>
+        <v>0.4775317699462859</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1773,55 +1773,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>230.4</v>
+        <v>1399.5</v>
       </c>
       <c r="V11">
-        <v>0.2436548223350254</v>
+        <v>0.1206704777671435</v>
       </c>
       <c r="W11">
-        <v>0.006575263107077338</v>
+        <v>0.1014959111761186</v>
       </c>
       <c r="X11">
-        <v>0.06288792392089979</v>
+        <v>0.08943080727909815</v>
       </c>
       <c r="Y11">
-        <v>-0.05631266081382245</v>
+        <v>0.01206510389702045</v>
       </c>
       <c r="Z11">
-        <v>0.08875433421311391</v>
+        <v>0.09608676048316286</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.0601211766328185</v>
+        <v>0.06668399619228954</v>
       </c>
       <c r="AC11">
-        <v>-0.0601211766328185</v>
+        <v>-0.06668399619228954</v>
       </c>
       <c r="AD11">
-        <v>138.7</v>
+        <v>16808.9</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>138.7</v>
+        <v>16808.9</v>
       </c>
       <c r="AG11">
-        <v>-91.70000000000002</v>
+        <v>15409.4</v>
       </c>
       <c r="AH11">
-        <v>0.1279166282394171</v>
+        <v>0.5917251624622447</v>
       </c>
       <c r="AI11">
-        <v>0.1203470715835141</v>
+        <v>0.6681466759415682</v>
       </c>
       <c r="AJ11">
-        <v>-0.1073896240777609</v>
+        <v>0.5705684801404075</v>
       </c>
       <c r="AK11">
-        <v>-0.09944691465133937</v>
+        <v>0.6485983668658979</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chang Hwa Commercial Bank, Ltd. (TWSE:2801)</t>
+          <t>Taishin Financial Holding Co., Ltd. (TWSE:2887)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0304</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E12">
-        <v>-0.00031</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1865,28 +1865,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>394.3</v>
+        <v>603.2</v>
       </c>
       <c r="L12">
-        <v>0.3637453874538745</v>
+        <v>0.3281292498504053</v>
       </c>
       <c r="M12">
-        <v>181.1</v>
+        <v>235.7</v>
       </c>
       <c r="N12">
-        <v>0.02854755824584634</v>
+        <v>0.03421992508493277</v>
       </c>
       <c r="O12">
-        <v>0.4592949530814101</v>
+        <v>0.3907493368700265</v>
       </c>
       <c r="P12">
-        <v>181.1</v>
+        <v>235.7</v>
       </c>
       <c r="Q12">
-        <v>0.02854755824584634</v>
+        <v>0.03421992508493277</v>
       </c>
       <c r="R12">
-        <v>0.4592949530814101</v>
+        <v>0.3907493368700265</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1895,917 +1895,60 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>3207.7</v>
+        <v>3227.4</v>
       </c>
       <c r="V12">
-        <v>0.5056433052744411</v>
+        <v>0.4685676123000087</v>
       </c>
       <c r="W12">
-        <v>0.07520073236320637</v>
+        <v>0.09773485855017985</v>
       </c>
       <c r="X12">
-        <v>0.07515092266995632</v>
+        <v>0.09536044013185979</v>
       </c>
       <c r="Y12">
-        <v>4.980969325005247e-05</v>
+        <v>0.002374418418320062</v>
       </c>
       <c r="Z12">
-        <v>0.174678118503956</v>
+        <v>0.1088266635093535</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.06115630401253693</v>
+        <v>0.06674507299738625</v>
       </c>
       <c r="AC12">
-        <v>-0.06115630401253693</v>
+        <v>-0.06674507299738625</v>
       </c>
       <c r="AD12">
-        <v>5441.2</v>
+        <v>12509.5</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>5441.2</v>
+        <v>12509.5</v>
       </c>
       <c r="AG12">
-        <v>2233.5</v>
+        <v>9282.1</v>
       </c>
       <c r="AH12">
-        <v>0.4617055579126008</v>
+        <v>0.6449093430528992</v>
       </c>
       <c r="AI12">
-        <v>0.4918332113060535</v>
+        <v>0.6375502008032128</v>
       </c>
       <c r="AJ12">
-        <v>0.2603966283096079</v>
+        <v>0.574035708322253</v>
       </c>
       <c r="AK12">
-        <v>0.2843267051964254</v>
+        <v>0.5661957569324989</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>The Shanghai Commercial &amp; Savings Bank, Ltd. (TWSE:5876)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.0436</v>
-      </c>
-      <c r="E13">
-        <v>0.0462</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>516.8</v>
-      </c>
-      <c r="L13">
-        <v>0.3769786271792253</v>
-      </c>
-      <c r="M13">
-        <v>21.3</v>
-      </c>
-      <c r="N13">
-        <v>0.002874998312794418</v>
-      </c>
-      <c r="O13">
-        <v>0.04121517027863777</v>
-      </c>
-      <c r="P13">
-        <v>21.3</v>
-      </c>
-      <c r="Q13">
-        <v>0.002874998312794418</v>
-      </c>
-      <c r="R13">
-        <v>0.04121517027863777</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>1460.3</v>
-      </c>
-      <c r="V13">
-        <v>0.1971061049846802</v>
-      </c>
-      <c r="W13">
-        <v>0.107331256490135</v>
-      </c>
-      <c r="X13">
-        <v>0.07032037237638175</v>
-      </c>
-      <c r="Y13">
-        <v>0.03701088411375324</v>
-      </c>
-      <c r="Z13">
-        <v>0.1872691408213669</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.06177288753711747</v>
-      </c>
-      <c r="AC13">
-        <v>-0.06177288753711747</v>
-      </c>
-      <c r="AD13">
-        <v>4279.5</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>4279.5</v>
-      </c>
-      <c r="AG13">
-        <v>2819.2</v>
-      </c>
-      <c r="AH13">
-        <v>0.3661384986567649</v>
-      </c>
-      <c r="AI13">
-        <v>0.3601363292097955</v>
-      </c>
-      <c r="AJ13">
-        <v>0.275638205301186</v>
-      </c>
-      <c r="AK13">
-        <v>0.2704865341993917</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Taiwan Business Bank, Ltd. (TWSE:2834)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>0.0733</v>
-      </c>
-      <c r="E14">
-        <v>0.124</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>354.3</v>
-      </c>
-      <c r="L14">
-        <v>0.3940607273940607</v>
-      </c>
-      <c r="M14">
-        <v>24.1</v>
-      </c>
-      <c r="N14">
-        <v>0.006554790981042784</v>
-      </c>
-      <c r="O14">
-        <v>0.06802145074795371</v>
-      </c>
-      <c r="P14">
-        <v>24.1</v>
-      </c>
-      <c r="Q14">
-        <v>0.006554790981042784</v>
-      </c>
-      <c r="R14">
-        <v>0.06802145074795371</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>1263.4</v>
-      </c>
-      <c r="V14">
-        <v>0.343623357902467</v>
-      </c>
-      <c r="W14">
-        <v>0.11319127184435</v>
-      </c>
-      <c r="X14">
-        <v>0.07774831311653563</v>
-      </c>
-      <c r="Y14">
-        <v>0.0354429587278144</v>
-      </c>
-      <c r="Z14">
-        <v>0.1525268461499313</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0.0622981049937998</v>
-      </c>
-      <c r="AC14">
-        <v>-0.0622981049937998</v>
-      </c>
-      <c r="AD14">
-        <v>3707.3</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>3707.3</v>
-      </c>
-      <c r="AG14">
-        <v>2443.9</v>
-      </c>
-      <c r="AH14">
-        <v>0.5020720476706393</v>
-      </c>
-      <c r="AI14">
-        <v>0.5087204116638079</v>
-      </c>
-      <c r="AJ14">
-        <v>0.399290919190929</v>
-      </c>
-      <c r="AK14">
-        <v>0.405687156587706</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Taiwan Cooperative Financial Holding Co., Ltd. (TWSE:5880)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>0.0613</v>
-      </c>
-      <c r="E15">
-        <v>0.06059999999999999</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>619.9</v>
-      </c>
-      <c r="L15">
-        <v>0.3546541564162709</v>
-      </c>
-      <c r="M15">
-        <v>217.7</v>
-      </c>
-      <c r="N15">
-        <v>0.01698300139639745</v>
-      </c>
-      <c r="O15">
-        <v>0.3511856751088885</v>
-      </c>
-      <c r="P15">
-        <v>217.7</v>
-      </c>
-      <c r="Q15">
-        <v>0.01698300139639745</v>
-      </c>
-      <c r="R15">
-        <v>0.3511856751088885</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>2164.9</v>
-      </c>
-      <c r="V15">
-        <v>0.1688860804917815</v>
-      </c>
-      <c r="W15">
-        <v>0.09770359512664113</v>
-      </c>
-      <c r="X15">
-        <v>0.07355465022183547</v>
-      </c>
-      <c r="Y15">
-        <v>0.02414894490480567</v>
-      </c>
-      <c r="Z15">
-        <v>0.1371299906639574</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0.06249603800958611</v>
-      </c>
-      <c r="AC15">
-        <v>-0.06249603800958611</v>
-      </c>
-      <c r="AD15">
-        <v>9808.4</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>9808.4</v>
-      </c>
-      <c r="AG15">
-        <v>7643.5</v>
-      </c>
-      <c r="AH15">
-        <v>0.4334802073619686</v>
-      </c>
-      <c r="AI15">
-        <v>0.5736107699685369</v>
-      </c>
-      <c r="AJ15">
-        <v>0.3735424343423483</v>
-      </c>
-      <c r="AK15">
-        <v>0.5118015333623489</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>E.SUN Financial Holding Company, Ltd. (TWSE:2884)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>0.0613</v>
-      </c>
-      <c r="E16">
-        <v>0.0388</v>
-      </c>
-      <c r="F16">
-        <v>0.134</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>621.3</v>
-      </c>
-      <c r="L16">
-        <v>0.32562893081761</v>
-      </c>
-      <c r="M16">
-        <v>88.7</v>
-      </c>
-      <c r="N16">
-        <v>0.006724587578845222</v>
-      </c>
-      <c r="O16">
-        <v>0.1427651698052471</v>
-      </c>
-      <c r="P16">
-        <v>88.7</v>
-      </c>
-      <c r="Q16">
-        <v>0.006724587578845222</v>
-      </c>
-      <c r="R16">
-        <v>0.1427651698052471</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>1715.3</v>
-      </c>
-      <c r="V16">
-        <v>0.130041545366327</v>
-      </c>
-      <c r="W16">
-        <v>0.106514657980456</v>
-      </c>
-      <c r="X16">
-        <v>0.07391655402821035</v>
-      </c>
-      <c r="Y16">
-        <v>0.03259810395224567</v>
-      </c>
-      <c r="Z16">
-        <v>0.1356742112336541</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0.062528862050096</v>
-      </c>
-      <c r="AC16">
-        <v>-0.062528862050096</v>
-      </c>
-      <c r="AD16">
-        <v>10369.6</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>10369.6</v>
-      </c>
-      <c r="AG16">
-        <v>8654.300000000001</v>
-      </c>
-      <c r="AH16">
-        <v>0.4401358234295416</v>
-      </c>
-      <c r="AI16">
-        <v>0.5933521397549825</v>
-      </c>
-      <c r="AJ16">
-        <v>0.3961739003053373</v>
-      </c>
-      <c r="AK16">
-        <v>0.5490958695514244</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>First Financial Holding Co., Ltd. (TWSE:2892)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>0.0405</v>
-      </c>
-      <c r="E17">
-        <v>0.09179999999999999</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>720.8</v>
-      </c>
-      <c r="L17">
-        <v>0.3797881869434638</v>
-      </c>
-      <c r="M17">
-        <v>328.7</v>
-      </c>
-      <c r="N17">
-        <v>0.02698553437433296</v>
-      </c>
-      <c r="O17">
-        <v>0.4560210876803552</v>
-      </c>
-      <c r="P17">
-        <v>328.7</v>
-      </c>
-      <c r="Q17">
-        <v>0.02698553437433296</v>
-      </c>
-      <c r="R17">
-        <v>0.4560210876803552</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>1828.6</v>
-      </c>
-      <c r="V17">
-        <v>0.1501239676206426</v>
-      </c>
-      <c r="W17">
-        <v>0.1053909025777492</v>
-      </c>
-      <c r="X17">
-        <v>0.08213142226910891</v>
-      </c>
-      <c r="Y17">
-        <v>0.02325948030864027</v>
-      </c>
-      <c r="Z17">
-        <v>0.1577862208292111</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0.06311016461286</v>
-      </c>
-      <c r="AC17">
-        <v>-0.06311016461286</v>
-      </c>
-      <c r="AD17">
-        <v>15377.6</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>15377.6</v>
-      </c>
-      <c r="AG17">
-        <v>13549</v>
-      </c>
-      <c r="AH17">
-        <v>0.5580045140829227</v>
-      </c>
-      <c r="AI17">
-        <v>0.6715666365331622</v>
-      </c>
-      <c r="AJ17">
-        <v>0.5265919407997015</v>
-      </c>
-      <c r="AK17">
-        <v>0.6430622463750919</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SinoPac Financial Holdings Company Limited (TWSE:2890)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>0.09300000000000001</v>
-      </c>
-      <c r="E18">
-        <v>0.13</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>582.3</v>
-      </c>
-      <c r="L18">
-        <v>0.3798682236284167</v>
-      </c>
-      <c r="M18">
-        <v>226.2</v>
-      </c>
-      <c r="N18">
-        <v>0.028401742777143</v>
-      </c>
-      <c r="O18">
-        <v>0.3884595569294179</v>
-      </c>
-      <c r="P18">
-        <v>226.2</v>
-      </c>
-      <c r="Q18">
-        <v>0.028401742777143</v>
-      </c>
-      <c r="R18">
-        <v>0.3884595569294179</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>988.3</v>
-      </c>
-      <c r="V18">
-        <v>0.124091257235413</v>
-      </c>
-      <c r="W18">
-        <v>0.1253282252163058</v>
-      </c>
-      <c r="X18">
-        <v>0.08568051616746755</v>
-      </c>
-      <c r="Y18">
-        <v>0.03964770904883824</v>
-      </c>
-      <c r="Z18">
-        <v>0.109224476999373</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0.06329190311096147</v>
-      </c>
-      <c r="AC18">
-        <v>-0.06329190311096147</v>
-      </c>
-      <c r="AD18">
-        <v>11693.6</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>11693.6</v>
-      </c>
-      <c r="AG18">
-        <v>10705.3</v>
-      </c>
-      <c r="AH18">
-        <v>0.594854994684071</v>
-      </c>
-      <c r="AI18">
-        <v>0.6786018953220481</v>
-      </c>
-      <c r="AJ18">
-        <v>0.5734081072974246</v>
-      </c>
-      <c r="AK18">
-        <v>0.6590472555344874</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Taishin Financial Holding Co., Ltd. (TWSE:2887)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>0.0727</v>
-      </c>
-      <c r="E19">
-        <v>0.0607</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>580.9</v>
-      </c>
-      <c r="L19">
-        <v>0.3506791427709025</v>
-      </c>
-      <c r="M19">
-        <v>353.8</v>
-      </c>
-      <c r="N19">
-        <v>0.04410976324352629</v>
-      </c>
-      <c r="O19">
-        <v>0.6090549147873989</v>
-      </c>
-      <c r="P19">
-        <v>189.8</v>
-      </c>
-      <c r="Q19">
-        <v>0.02366317994240048</v>
-      </c>
-      <c r="R19">
-        <v>0.3267343776897917</v>
-      </c>
-      <c r="S19">
-        <v>164</v>
-      </c>
-      <c r="T19">
-        <v>0.4635387224420576</v>
-      </c>
-      <c r="U19">
-        <v>1517.1</v>
-      </c>
-      <c r="V19">
-        <v>0.1891433629642559</v>
-      </c>
-      <c r="W19">
-        <v>0.1011686027273202</v>
-      </c>
-      <c r="X19">
-        <v>0.08604066865001087</v>
-      </c>
-      <c r="Y19">
-        <v>0.01512793407730936</v>
-      </c>
-      <c r="Z19">
-        <v>0.09618008581597756</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0.06330866602955332</v>
-      </c>
-      <c r="AC19">
-        <v>-0.06330866602955332</v>
-      </c>
-      <c r="AD19">
-        <v>11944.2</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>11944.2</v>
-      </c>
-      <c r="AG19">
-        <v>10427.1</v>
-      </c>
-      <c r="AH19">
-        <v>0.5982539531482438</v>
-      </c>
-      <c r="AI19">
-        <v>0.6470769880869184</v>
-      </c>
-      <c r="AJ19">
-        <v>0.5652157415437988</v>
-      </c>
-      <c r="AK19">
-        <v>0.6154731548377957</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/taiwan/taiwan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,106 +588,106 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06320000000000001</v>
+        <v>0.0624</v>
       </c>
       <c r="E2">
-        <v>0.06795</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F2">
         <v>0.06235</v>
       </c>
       <c r="G2">
-        <v>0.1647696163616763</v>
+        <v>0.1365528514859857</v>
       </c>
       <c r="H2">
-        <v>0.1647696163616763</v>
+        <v>0.1365528514859857</v>
       </c>
       <c r="I2">
-        <v>0.2115518435809536</v>
+        <v>0.1753236313586239</v>
       </c>
       <c r="J2">
-        <v>0.1732559904825418</v>
+        <v>0.1455072434669147</v>
       </c>
       <c r="K2">
-        <v>6861.099999999999</v>
+        <v>9389.299999999999</v>
       </c>
       <c r="L2">
-        <v>0.2333286856451048</v>
+        <v>0.2646252272310922</v>
       </c>
       <c r="M2">
-        <v>3462.4</v>
+        <v>4887.13</v>
       </c>
       <c r="N2">
-        <v>0.0371531246546135</v>
+        <v>0.03760001784933927</v>
       </c>
       <c r="O2">
-        <v>0.5046421127807494</v>
+        <v>0.5204999307722621</v>
       </c>
       <c r="P2">
-        <v>3462.4</v>
+        <v>4885.7</v>
       </c>
       <c r="Q2">
-        <v>0.0371531246546135</v>
+        <v>0.03758901588591194</v>
       </c>
       <c r="R2">
-        <v>0.5046421127807494</v>
+        <v>0.5203476297487566</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.0002926052713965046</v>
       </c>
       <c r="U2">
-        <v>21160.5</v>
+        <v>28113</v>
       </c>
       <c r="V2">
-        <v>0.2270617762979289</v>
+        <v>0.2162924460365234</v>
       </c>
       <c r="W2">
-        <v>0.09752392891198172</v>
+        <v>0.09773485855017985</v>
       </c>
       <c r="X2">
-        <v>0.08098469052821072</v>
+        <v>0.08110800526338816</v>
       </c>
       <c r="Y2">
-        <v>0.016539238383771</v>
+        <v>0.0166268532867917</v>
       </c>
       <c r="Z2">
-        <v>0.2331870836908492</v>
+        <v>0.1868942297299768</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06655326317559815</v>
+        <v>0.06600620972871539</v>
       </c>
       <c r="AC2">
-        <v>-0.06628233193915622</v>
+        <v>-0.06520536879401466</v>
       </c>
       <c r="AD2">
-        <v>98156.60000000001</v>
+        <v>147723.1</v>
       </c>
       <c r="AE2">
         <v>110.2728697449233</v>
       </c>
       <c r="AF2">
-        <v>98266.87286974493</v>
+        <v>147833.3728697449</v>
       </c>
       <c r="AG2">
-        <v>77106.37286974493</v>
+        <v>119720.3728697449</v>
       </c>
       <c r="AH2">
-        <v>0.513251290582365</v>
+        <v>0.5321380831473677</v>
       </c>
       <c r="AI2">
-        <v>0.5673774935800133</v>
+        <v>0.5906720029360197</v>
       </c>
       <c r="AJ2">
-        <v>0.4527703619897013</v>
+        <v>0.4794622682099701</v>
       </c>
       <c r="AK2">
-        <v>0.5071640801636721</v>
+        <v>0.5388756543031993</v>
       </c>
       <c r="AL2">
         <v>3408.9</v>
@@ -696,13 +696,13 @@
         <v>3408.9</v>
       </c>
       <c r="AN2">
-        <v>15.45919299461366</v>
+        <v>23.26567864680127</v>
       </c>
       <c r="AO2">
         <v>1.813341547126639</v>
       </c>
       <c r="AP2">
-        <v>12.143883338543</v>
+        <v>18.85538363778387</v>
       </c>
       <c r="AQ2">
         <v>1.813341547126639</v>
@@ -785,10 +785,10 @@
         <v>0.1640359168241966</v>
       </c>
       <c r="X3">
-        <v>0.07843480419395102</v>
+        <v>0.07841956341864775</v>
       </c>
       <c r="Y3">
-        <v>0.08560111263024558</v>
+        <v>0.08561635340554885</v>
       </c>
       <c r="Z3">
         <v>1.09190442765322</v>
@@ -797,10 +797,10 @@
         <v>0.3505120685328191</v>
       </c>
       <c r="AB3">
-        <v>0.06650369121266977</v>
+        <v>0.06649507590748316</v>
       </c>
       <c r="AC3">
-        <v>0.2840083773201493</v>
+        <v>0.2840169926253359</v>
       </c>
       <c r="AD3">
         <v>17997.8</v>
@@ -919,10 +919,10 @@
         <v>0.07878543326944416</v>
       </c>
       <c r="X4">
-        <v>0.092889172221505</v>
+        <v>0.09286718111382808</v>
       </c>
       <c r="Y4">
-        <v>-0.01410373895206084</v>
+        <v>-0.01408174784438392</v>
       </c>
       <c r="Z4">
         <v>0.1246704236757948</v>
@@ -931,10 +931,10 @@
         <v>0.00698101539881465</v>
       </c>
       <c r="AB4">
-        <v>0.06672166322969861</v>
+        <v>0.06671340611178729</v>
       </c>
       <c r="AC4">
-        <v>-0.05974064783088396</v>
+        <v>-0.05973239071297264</v>
       </c>
       <c r="AD4">
         <v>3023.7</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chang Hwa Commercial Bank, Ltd. (TWSE:2801)</t>
+          <t>O-Bank Co., Ltd. (TWSE:2897)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0417</v>
+        <v>0.0398</v>
       </c>
       <c r="E5">
-        <v>0.0372</v>
+        <v>0.155</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1008,85 +1008,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>440.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L5">
-        <v>0.3742779476724431</v>
+        <v>0.2848275862068965</v>
       </c>
       <c r="M5">
-        <v>188</v>
+        <v>40.13</v>
       </c>
       <c r="N5">
-        <v>0.03081007555023845</v>
+        <v>0.04754739336492891</v>
       </c>
       <c r="O5">
-        <v>0.4266908760780753</v>
+        <v>0.4858353510895884</v>
       </c>
       <c r="P5">
-        <v>188</v>
+        <v>38.7</v>
       </c>
       <c r="Q5">
-        <v>0.03081007555023845</v>
+        <v>0.04585308056872038</v>
       </c>
       <c r="R5">
-        <v>0.4266908760780753</v>
+        <v>0.4685230024213076</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.0356341888861201</v>
       </c>
       <c r="U5">
-        <v>4300</v>
+        <v>406.5</v>
       </c>
       <c r="V5">
-        <v>0.7046985365214115</v>
+        <v>0.4816350710900474</v>
       </c>
       <c r="W5">
-        <v>0.0783720806133158</v>
+        <v>0.0730779439086968</v>
       </c>
       <c r="X5">
-        <v>0.08084487890226502</v>
+        <v>0.2323732928413301</v>
       </c>
       <c r="Y5">
-        <v>-0.002472798288949224</v>
+        <v>-0.1592953489326333</v>
       </c>
       <c r="Z5">
-        <v>0.1498586959289152</v>
+        <v>0.03644910322637407</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06521390117528393</v>
+        <v>0.06266834527037141</v>
       </c>
       <c r="AC5">
-        <v>-0.06521390117528393</v>
+        <v>-0.06266834527037141</v>
       </c>
       <c r="AD5">
-        <v>5602.4</v>
+        <v>8691.700000000001</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>5602.4</v>
+        <v>8691.700000000001</v>
       </c>
       <c r="AG5">
-        <v>1302.4</v>
+        <v>8285.200000000001</v>
       </c>
       <c r="AH5">
-        <v>0.4786616884392915</v>
+        <v>0.9114905041056242</v>
       </c>
       <c r="AI5">
-        <v>0.4710392897079966</v>
+        <v>0.8129161990273102</v>
       </c>
       <c r="AJ5">
-        <v>0.1758977891225369</v>
+        <v>0.9075494019191167</v>
       </c>
       <c r="AK5">
-        <v>0.1715105943084398</v>
+        <v>0.8055223372709155</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Shanghai Commercial &amp; Savings Bank, Ltd. (TWSE:5876)</t>
+          <t>Hua Nan Financial Holdings Co., Ltd. (TWSE:2880)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0418</v>
+        <v>0.063</v>
       </c>
       <c r="E6">
-        <v>-0.0659</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1130,28 +1130,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>331.5</v>
+        <v>711</v>
       </c>
       <c r="L6">
-        <v>0.3249044398706263</v>
+        <v>0.3677839851024208</v>
       </c>
       <c r="M6">
-        <v>275.2</v>
+        <v>513.8</v>
       </c>
       <c r="N6">
-        <v>0.04696806785793525</v>
+        <v>0.04674266063809462</v>
       </c>
       <c r="O6">
-        <v>0.8301659125188536</v>
+        <v>0.7226441631504922</v>
       </c>
       <c r="P6">
-        <v>275.2</v>
+        <v>513.8</v>
       </c>
       <c r="Q6">
-        <v>0.04696806785793525</v>
+        <v>0.04674266063809462</v>
       </c>
       <c r="R6">
-        <v>0.8301659125188536</v>
+        <v>0.7226441631504922</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1160,55 +1160,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1303.4</v>
+        <v>2031.7</v>
       </c>
       <c r="V6">
-        <v>0.2224497806905262</v>
+        <v>0.1848327435157977</v>
       </c>
       <c r="W6">
-        <v>0.05874638926792961</v>
+        <v>0.1169254045520326</v>
       </c>
       <c r="X6">
-        <v>0.07547120500680471</v>
+        <v>0.0879023067800494</v>
       </c>
       <c r="Y6">
-        <v>-0.0167248157388751</v>
+        <v>0.02902309777198323</v>
       </c>
       <c r="Z6">
-        <v>0.1206159535079465</v>
+        <v>0.09481843632960639</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06601494838198529</v>
+        <v>0.06389443578341947</v>
       </c>
       <c r="AC6">
-        <v>-0.06601494838198529</v>
+        <v>-0.06389443578341947</v>
       </c>
       <c r="AD6">
-        <v>3431.7</v>
+        <v>14905.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>3431.7</v>
+        <v>14905.1</v>
       </c>
       <c r="AG6">
-        <v>2128.3</v>
+        <v>12873.4</v>
       </c>
       <c r="AH6">
-        <v>0.3693574426864707</v>
+        <v>0.5755487079684291</v>
       </c>
       <c r="AI6">
-        <v>0.2956374162201278</v>
+        <v>0.6843354575673541</v>
       </c>
       <c r="AJ6">
-        <v>0.266450498272322</v>
+        <v>0.5394146361903166</v>
       </c>
       <c r="AK6">
-        <v>0.2065428360700283</v>
+        <v>0.651860628800883</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Taiwan Business Bank, Ltd. (TWSE:2834)</t>
+          <t>Mega Financial Holding Co., Ltd. (TWSE:2886)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.064</v>
+        <v>0.0447</v>
       </c>
       <c r="E7">
-        <v>0.09480000000000001</v>
+        <v>0.04940000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1252,28 +1252,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>348.4</v>
+        <v>1119</v>
       </c>
       <c r="L7">
-        <v>0.3808482728465238</v>
+        <v>0.4594916437399909</v>
       </c>
       <c r="M7">
-        <v>77.09999999999999</v>
+        <v>611.8</v>
       </c>
       <c r="N7">
-        <v>0.01856399884426466</v>
+        <v>0.03493604385564184</v>
       </c>
       <c r="O7">
-        <v>0.2212973593570609</v>
+        <v>0.5467381590705988</v>
       </c>
       <c r="P7">
-        <v>77.09999999999999</v>
+        <v>611.8</v>
       </c>
       <c r="Q7">
-        <v>0.01856399884426466</v>
+        <v>0.03493604385564184</v>
       </c>
       <c r="R7">
-        <v>0.2212973593570609</v>
+        <v>0.5467381590705988</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1282,55 +1282,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>914.8</v>
+        <v>2251.5</v>
       </c>
       <c r="V7">
-        <v>0.2202638929018588</v>
+        <v>0.1285689812699863</v>
       </c>
       <c r="W7">
-        <v>0.09731299927378359</v>
+        <v>0.1131057068348596</v>
       </c>
       <c r="X7">
-        <v>0.08000961305715337</v>
+        <v>0.08521738075398735</v>
       </c>
       <c r="Y7">
-        <v>0.01730338621663022</v>
+        <v>0.02788832608087226</v>
       </c>
       <c r="Z7">
-        <v>0.1518567088859747</v>
+        <v>0.09353802899129647</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06601764286054923</v>
+        <v>0.0640120015229147</v>
       </c>
       <c r="AC7">
-        <v>-0.06601764286054923</v>
+        <v>-0.0640120015229147</v>
       </c>
       <c r="AD7">
-        <v>3598.6</v>
+        <v>20835.7</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3598.6</v>
+        <v>20835.7</v>
       </c>
       <c r="AG7">
-        <v>2683.8</v>
+        <v>18584.2</v>
       </c>
       <c r="AH7">
-        <v>0.4642276632524059</v>
+        <v>0.5433363669789845</v>
       </c>
       <c r="AI7">
-        <v>0.467144377807202</v>
+        <v>0.6466978701743714</v>
       </c>
       <c r="AJ7">
-        <v>0.392540587977183</v>
+        <v>0.5148519788786632</v>
       </c>
       <c r="AK7">
-        <v>0.395339245205197</v>
+        <v>0.6201534349336439</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E.SUN Financial Holding Company, Ltd. (TWSE:2884)</t>
+          <t>Far Eastern International Bank Ltd. (TWSE:2845)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1356,13 +1356,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.07339999999999999</v>
+        <v>0.0206</v>
       </c>
       <c r="E8">
-        <v>0.0649</v>
-      </c>
-      <c r="F8">
-        <v>0.0339</v>
+        <v>0.0225</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1377,28 +1374,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>842</v>
+        <v>134.4</v>
       </c>
       <c r="L8">
-        <v>0.3708597603946441</v>
+        <v>0.3376036171816126</v>
       </c>
       <c r="M8">
-        <v>591.8</v>
+        <v>64.8</v>
       </c>
       <c r="N8">
-        <v>0.0450014067692214</v>
+        <v>0.03763940520446097</v>
       </c>
       <c r="O8">
-        <v>0.7028503562945367</v>
+        <v>0.4821428571428571</v>
       </c>
       <c r="P8">
-        <v>591.8</v>
+        <v>64.8</v>
       </c>
       <c r="Q8">
-        <v>0.0450014067692214</v>
+        <v>0.03763940520446097</v>
       </c>
       <c r="R8">
-        <v>0.7028503562945367</v>
+        <v>0.4821428571428571</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1407,55 +1404,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>2041.9</v>
+        <v>1313.1</v>
       </c>
       <c r="V8">
-        <v>0.1552693012539257</v>
+        <v>0.7627207249070632</v>
       </c>
       <c r="W8">
-        <v>0.1185648304607412</v>
+        <v>0.07493727348759409</v>
       </c>
       <c r="X8">
-        <v>0.080479851249158</v>
+        <v>0.0850836351725576</v>
       </c>
       <c r="Y8">
-        <v>0.03808497921158323</v>
+        <v>-0.01014636168496351</v>
       </c>
       <c r="Z8">
-        <v>0.1453939995517274</v>
+        <v>0.1476412995104584</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06654702101776321</v>
+        <v>0.06401832624429099</v>
       </c>
       <c r="AC8">
-        <v>-0.06654702101776321</v>
+        <v>-0.06401832624429099</v>
       </c>
       <c r="AD8">
-        <v>11777.2</v>
+        <v>2034.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>11777.2</v>
+        <v>2034.1</v>
       </c>
       <c r="AG8">
-        <v>9735.300000000001</v>
+        <v>721</v>
       </c>
       <c r="AH8">
-        <v>0.47245054737864</v>
+        <v>0.5416034294538967</v>
       </c>
       <c r="AI8">
-        <v>0.6017679219252977</v>
+        <v>0.5162952434133712</v>
       </c>
       <c r="AJ8">
-        <v>0.4253823298086167</v>
+        <v>0.2951772701220012</v>
       </c>
       <c r="AK8">
-        <v>0.5553793406392799</v>
+        <v>0.2744889024250962</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1472,7 +1469,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Taiwan Cooperative Financial Holding Co., Ltd. (TWSE:5880)</t>
+          <t>King's Town Bank Co., Ltd. (TWSE:2809)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1481,10 +1478,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0624</v>
+        <v>0.231</v>
       </c>
       <c r="E9">
-        <v>0.0268</v>
+        <v>0.35</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1499,28 +1496,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>584.8</v>
+        <v>175.5</v>
       </c>
       <c r="L9">
-        <v>0.3188137164040779</v>
+        <v>0.5809334657398212</v>
       </c>
       <c r="M9">
-        <v>301</v>
+        <v>105</v>
       </c>
       <c r="N9">
-        <v>0.02667115616360672</v>
+        <v>0.06109268633269331</v>
       </c>
       <c r="O9">
-        <v>0.5147058823529412</v>
+        <v>0.5982905982905983</v>
       </c>
       <c r="P9">
-        <v>301</v>
+        <v>105</v>
       </c>
       <c r="Q9">
-        <v>0.02667115616360672</v>
+        <v>0.06109268633269331</v>
       </c>
       <c r="R9">
-        <v>0.5147058823529412</v>
+        <v>0.5982905982905983</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1529,55 +1526,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>2112.6</v>
+        <v>398.8</v>
       </c>
       <c r="V9">
-        <v>0.1871943007017793</v>
+        <v>0.2320358410426485</v>
       </c>
       <c r="W9">
-        <v>0.08213483146067416</v>
+        <v>0.1216975244435199</v>
       </c>
       <c r="X9">
-        <v>0.08112450215415642</v>
+        <v>0.07591216830947931</v>
       </c>
       <c r="Y9">
-        <v>0.001010329306517732</v>
+        <v>0.04578535613404057</v>
       </c>
       <c r="Z9">
-        <v>0.124982965849936</v>
+        <v>0.1337021464925869</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06655950533343309</v>
+        <v>0.06460682414705297</v>
       </c>
       <c r="AC9">
-        <v>-0.06655950533343309</v>
+        <v>-0.06460682414705297</v>
       </c>
       <c r="AD9">
-        <v>10557</v>
+        <v>1055</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>10557</v>
+        <v>1055</v>
       </c>
       <c r="AG9">
-        <v>8444.4</v>
+        <v>656.2</v>
       </c>
       <c r="AH9">
-        <v>0.4833215825954786</v>
+        <v>0.3803583660814076</v>
       </c>
       <c r="AI9">
-        <v>0.5634486881151128</v>
+        <v>0.3827733836441478</v>
       </c>
       <c r="AJ9">
-        <v>0.4279979726305119</v>
+        <v>0.2763063707945598</v>
       </c>
       <c r="AK9">
-        <v>0.5079705001263249</v>
+        <v>0.2783575125137864</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1594,7 +1591,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SinoPac Financial Holdings Company Limited (TWSE:2890)</t>
+          <t>Taichung Commercial Bank Co., Ltd. (TWSE:2812)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1603,10 +1600,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.122</v>
+        <v>0.0925</v>
       </c>
       <c r="E10">
-        <v>0.153</v>
+        <v>0.147</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1621,28 +1618,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>708.5</v>
+        <v>260.2</v>
       </c>
       <c r="L10">
-        <v>0.3800761761708063</v>
+        <v>0.4640627786695202</v>
       </c>
       <c r="M10">
-        <v>292.3</v>
+        <v>65.8</v>
       </c>
       <c r="N10">
-        <v>0.03295674919947684</v>
+        <v>0.02084455285583046</v>
       </c>
       <c r="O10">
-        <v>0.4125617501764291</v>
+        <v>0.2528823981552652</v>
       </c>
       <c r="P10">
-        <v>292.3</v>
+        <v>65.8</v>
       </c>
       <c r="Q10">
-        <v>0.03295674919947684</v>
+        <v>0.02084455285583046</v>
       </c>
       <c r="R10">
-        <v>0.4125617501764291</v>
+        <v>0.2528823981552652</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1651,55 +1648,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1418.8</v>
+        <v>328.7</v>
       </c>
       <c r="V10">
-        <v>0.1599693320705362</v>
+        <v>0.1041277283238825</v>
       </c>
       <c r="W10">
-        <v>0.1279273423252623</v>
+        <v>0.1142330318728598</v>
       </c>
       <c r="X10">
-        <v>0.08942242076477458</v>
+        <v>0.0753374352662948</v>
       </c>
       <c r="Y10">
-        <v>0.03850492156048768</v>
+        <v>0.03889559660656497</v>
       </c>
       <c r="Z10">
-        <v>0.1149983343409542</v>
+        <v>0.160548619860268</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06668389684972251</v>
+        <v>0.06465779850860973</v>
       </c>
       <c r="AC10">
-        <v>-0.06668389684972251</v>
+        <v>-0.06465779850860973</v>
       </c>
       <c r="AD10">
-        <v>12849.8</v>
+        <v>1825.4</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>12849.8</v>
+        <v>1825.4</v>
       </c>
       <c r="AG10">
-        <v>11431</v>
+        <v>1496.7</v>
       </c>
       <c r="AH10">
-        <v>0.5916386573967494</v>
+        <v>0.366391682222356</v>
       </c>
       <c r="AI10">
-        <v>0.6670889033095392</v>
+        <v>0.4152222373868341</v>
       </c>
       <c r="AJ10">
-        <v>0.5630979005132954</v>
+        <v>0.3216357931834788</v>
       </c>
       <c r="AK10">
-        <v>0.6406182574241889</v>
+        <v>0.3679655808236018</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1716,7 +1713,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>First Financial Holding Co., Ltd. (TWSE:2892)</t>
+          <t>Chang Hwa Commercial Bank, Ltd. (TWSE:2801)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1725,10 +1722,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0252</v>
+        <v>0.0417</v>
       </c>
       <c r="E11">
-        <v>0.0571</v>
+        <v>0.0372</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1743,28 +1740,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>763.3</v>
+        <v>440.6</v>
       </c>
       <c r="L11">
-        <v>0.3770313657693257</v>
+        <v>0.3742779476724431</v>
       </c>
       <c r="M11">
-        <v>364.5</v>
+        <v>188</v>
       </c>
       <c r="N11">
-        <v>0.03142864533485087</v>
+        <v>0.03081007555023845</v>
       </c>
       <c r="O11">
-        <v>0.4775317699462859</v>
+        <v>0.4266908760780753</v>
       </c>
       <c r="P11">
-        <v>364.5</v>
+        <v>188</v>
       </c>
       <c r="Q11">
-        <v>0.03142864533485087</v>
+        <v>0.03081007555023845</v>
       </c>
       <c r="R11">
-        <v>0.4775317699462859</v>
+        <v>0.4266908760780753</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1773,55 +1770,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1399.5</v>
+        <v>4300</v>
       </c>
       <c r="V11">
-        <v>0.1206704777671435</v>
+        <v>0.7046985365214115</v>
       </c>
       <c r="W11">
-        <v>0.1014959111761186</v>
+        <v>0.0783720806133158</v>
       </c>
       <c r="X11">
-        <v>0.08943080727909815</v>
+        <v>0.08082851259831217</v>
       </c>
       <c r="Y11">
-        <v>0.01206510389702045</v>
+        <v>-0.002456431984996371</v>
       </c>
       <c r="Z11">
-        <v>0.09608676048316286</v>
+        <v>0.1498586959289152</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06668399619228954</v>
+        <v>0.06520536879401466</v>
       </c>
       <c r="AC11">
-        <v>-0.06668399619228954</v>
+        <v>-0.06520536879401466</v>
       </c>
       <c r="AD11">
-        <v>16808.9</v>
+        <v>5602.4</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>16808.9</v>
+        <v>5602.4</v>
       </c>
       <c r="AG11">
-        <v>15409.4</v>
+        <v>1302.4</v>
       </c>
       <c r="AH11">
-        <v>0.5917251624622447</v>
+        <v>0.4786616884392915</v>
       </c>
       <c r="AI11">
-        <v>0.6681466759415682</v>
+        <v>0.4710392897079966</v>
       </c>
       <c r="AJ11">
-        <v>0.5705684801404075</v>
+        <v>0.1758977891225369</v>
       </c>
       <c r="AK11">
-        <v>0.6485983668658979</v>
+        <v>0.1715105943084398</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1838,117 +1835,974 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>EnTie Commercial Bank Co., Ltd. (TWSE:2849)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>-0.0294</v>
+      </c>
+      <c r="E12">
+        <v>-0.09570000000000001</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>45.5</v>
+      </c>
+      <c r="L12">
+        <v>0.2901785714285714</v>
+      </c>
+      <c r="M12">
+        <v>23.4</v>
+      </c>
+      <c r="N12">
+        <v>0.02789034564958284</v>
+      </c>
+      <c r="O12">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="P12">
+        <v>23.4</v>
+      </c>
+      <c r="Q12">
+        <v>0.02789034564958284</v>
+      </c>
+      <c r="R12">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>222.2</v>
+      </c>
+      <c r="V12">
+        <v>0.2648390941597139</v>
+      </c>
+      <c r="W12">
+        <v>0.0448806470704281</v>
+      </c>
+      <c r="X12">
+        <v>0.07022177548938427</v>
+      </c>
+      <c r="Y12">
+        <v>-0.02534112841895617</v>
+      </c>
+      <c r="Z12">
+        <v>0.1708377368357975</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.06523818566040093</v>
+      </c>
+      <c r="AC12">
+        <v>-0.06523818566040093</v>
+      </c>
+      <c r="AD12">
+        <v>219.5</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>219.5</v>
+      </c>
+      <c r="AG12">
+        <v>-2.699999999999989</v>
+      </c>
+      <c r="AH12">
+        <v>0.2073689182805857</v>
+      </c>
+      <c r="AI12">
+        <v>0.1685997388432291</v>
+      </c>
+      <c r="AJ12">
+        <v>-0.003228506516800178</v>
+      </c>
+      <c r="AK12">
+        <v>-0.002500694637399267</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Shanghai Commercial &amp; Savings Bank, Ltd. (TWSE:5876)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>-0.0418</v>
+      </c>
+      <c r="E13">
+        <v>-0.0659</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>331.5</v>
+      </c>
+      <c r="L13">
+        <v>0.3249044398706263</v>
+      </c>
+      <c r="M13">
+        <v>275.2</v>
+      </c>
+      <c r="N13">
+        <v>0.04696806785793525</v>
+      </c>
+      <c r="O13">
+        <v>0.8301659125188536</v>
+      </c>
+      <c r="P13">
+        <v>275.2</v>
+      </c>
+      <c r="Q13">
+        <v>0.04696806785793525</v>
+      </c>
+      <c r="R13">
+        <v>0.8301659125188536</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>1303.4</v>
+      </c>
+      <c r="V13">
+        <v>0.2224497806905262</v>
+      </c>
+      <c r="W13">
+        <v>0.05874638926792961</v>
+      </c>
+      <c r="X13">
+        <v>0.07545734826153978</v>
+      </c>
+      <c r="Y13">
+        <v>-0.01671095899361017</v>
+      </c>
+      <c r="Z13">
+        <v>0.1206159535079465</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.06600620972871539</v>
+      </c>
+      <c r="AC13">
+        <v>-0.06600620972871539</v>
+      </c>
+      <c r="AD13">
+        <v>3431.7</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>3431.7</v>
+      </c>
+      <c r="AG13">
+        <v>2128.3</v>
+      </c>
+      <c r="AH13">
+        <v>0.3693574426864707</v>
+      </c>
+      <c r="AI13">
+        <v>0.2956374162201278</v>
+      </c>
+      <c r="AJ13">
+        <v>0.266450498272322</v>
+      </c>
+      <c r="AK13">
+        <v>0.2065428360700283</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Taiwan Business Bank, Ltd. (TWSE:2834)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.064</v>
+      </c>
+      <c r="E14">
+        <v>0.09480000000000001</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>348.4</v>
+      </c>
+      <c r="L14">
+        <v>0.3808482728465238</v>
+      </c>
+      <c r="M14">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="N14">
+        <v>0.01856399884426466</v>
+      </c>
+      <c r="O14">
+        <v>0.2212973593570609</v>
+      </c>
+      <c r="P14">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="Q14">
+        <v>0.01856399884426466</v>
+      </c>
+      <c r="R14">
+        <v>0.2212973593570609</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>914.8</v>
+      </c>
+      <c r="V14">
+        <v>0.2202638929018588</v>
+      </c>
+      <c r="W14">
+        <v>0.09731299927378359</v>
+      </c>
+      <c r="X14">
+        <v>0.07999363683058504</v>
+      </c>
+      <c r="Y14">
+        <v>0.01731936244319855</v>
+      </c>
+      <c r="Z14">
+        <v>0.1518567088859747</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.06600908324030831</v>
+      </c>
+      <c r="AC14">
+        <v>-0.06600908324030831</v>
+      </c>
+      <c r="AD14">
+        <v>3598.6</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>3598.6</v>
+      </c>
+      <c r="AG14">
+        <v>2683.8</v>
+      </c>
+      <c r="AH14">
+        <v>0.4642276632524059</v>
+      </c>
+      <c r="AI14">
+        <v>0.467144377807202</v>
+      </c>
+      <c r="AJ14">
+        <v>0.392540587977183</v>
+      </c>
+      <c r="AK14">
+        <v>0.395339245205197</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>E.SUN Financial Holding Company, Ltd. (TWSE:2884)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.07339999999999999</v>
+      </c>
+      <c r="E15">
+        <v>0.0649</v>
+      </c>
+      <c r="F15">
+        <v>0.0339</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>842</v>
+      </c>
+      <c r="L15">
+        <v>0.3708597603946441</v>
+      </c>
+      <c r="M15">
+        <v>591.8</v>
+      </c>
+      <c r="N15">
+        <v>0.0450014067692214</v>
+      </c>
+      <c r="O15">
+        <v>0.7028503562945367</v>
+      </c>
+      <c r="P15">
+        <v>591.8</v>
+      </c>
+      <c r="Q15">
+        <v>0.0450014067692214</v>
+      </c>
+      <c r="R15">
+        <v>0.7028503562945367</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>2041.9</v>
+      </c>
+      <c r="V15">
+        <v>0.1552693012539257</v>
+      </c>
+      <c r="W15">
+        <v>0.1185648304607412</v>
+      </c>
+      <c r="X15">
+        <v>0.08046365541671795</v>
+      </c>
+      <c r="Y15">
+        <v>0.03810117504402329</v>
+      </c>
+      <c r="Z15">
+        <v>0.1453939995517274</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.0665384769152247</v>
+      </c>
+      <c r="AC15">
+        <v>-0.0665384769152247</v>
+      </c>
+      <c r="AD15">
+        <v>11777.2</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>11777.2</v>
+      </c>
+      <c r="AG15">
+        <v>9735.300000000001</v>
+      </c>
+      <c r="AH15">
+        <v>0.47245054737864</v>
+      </c>
+      <c r="AI15">
+        <v>0.6017679219252977</v>
+      </c>
+      <c r="AJ15">
+        <v>0.4253823298086167</v>
+      </c>
+      <c r="AK15">
+        <v>0.5553793406392799</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Taiwan Cooperative Financial Holding Co., Ltd. (TWSE:5880)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.0624</v>
+      </c>
+      <c r="E16">
+        <v>0.0268</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>584.8</v>
+      </c>
+      <c r="L16">
+        <v>0.3188137164040779</v>
+      </c>
+      <c r="M16">
+        <v>301</v>
+      </c>
+      <c r="N16">
+        <v>0.02667115616360672</v>
+      </c>
+      <c r="O16">
+        <v>0.5147058823529412</v>
+      </c>
+      <c r="P16">
+        <v>301</v>
+      </c>
+      <c r="Q16">
+        <v>0.02667115616360672</v>
+      </c>
+      <c r="R16">
+        <v>0.5147058823529412</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>2112.6</v>
+      </c>
+      <c r="V16">
+        <v>0.1871943007017793</v>
+      </c>
+      <c r="W16">
+        <v>0.08213483146067416</v>
+      </c>
+      <c r="X16">
+        <v>0.08110800526338816</v>
+      </c>
+      <c r="Y16">
+        <v>0.001026826197286002</v>
+      </c>
+      <c r="Z16">
+        <v>0.124982965849936</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.06655098174601884</v>
+      </c>
+      <c r="AC16">
+        <v>-0.06655098174601884</v>
+      </c>
+      <c r="AD16">
+        <v>10557</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>10557</v>
+      </c>
+      <c r="AG16">
+        <v>8444.4</v>
+      </c>
+      <c r="AH16">
+        <v>0.4833215825954786</v>
+      </c>
+      <c r="AI16">
+        <v>0.5634486881151128</v>
+      </c>
+      <c r="AJ16">
+        <v>0.4279979726305119</v>
+      </c>
+      <c r="AK16">
+        <v>0.5079705001263249</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SinoPac Financial Holdings Company Limited (TWSE:2890)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.122</v>
+      </c>
+      <c r="E17">
+        <v>0.153</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>708.5</v>
+      </c>
+      <c r="L17">
+        <v>0.3800761761708063</v>
+      </c>
+      <c r="M17">
+        <v>292.3</v>
+      </c>
+      <c r="N17">
+        <v>0.03295674919947684</v>
+      </c>
+      <c r="O17">
+        <v>0.4125617501764291</v>
+      </c>
+      <c r="P17">
+        <v>292.3</v>
+      </c>
+      <c r="Q17">
+        <v>0.03295674919947684</v>
+      </c>
+      <c r="R17">
+        <v>0.4125617501764291</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>1418.8</v>
+      </c>
+      <c r="V17">
+        <v>0.1599693320705362</v>
+      </c>
+      <c r="W17">
+        <v>0.1279273423252623</v>
+      </c>
+      <c r="X17">
+        <v>0.08940204866420644</v>
+      </c>
+      <c r="Y17">
+        <v>0.03852529366105582</v>
+      </c>
+      <c r="Z17">
+        <v>0.1149983343409542</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.06667557767138285</v>
+      </c>
+      <c r="AC17">
+        <v>-0.06667557767138285</v>
+      </c>
+      <c r="AD17">
+        <v>12849.8</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>12849.8</v>
+      </c>
+      <c r="AG17">
+        <v>11431</v>
+      </c>
+      <c r="AH17">
+        <v>0.5916386573967494</v>
+      </c>
+      <c r="AI17">
+        <v>0.6670889033095392</v>
+      </c>
+      <c r="AJ17">
+        <v>0.5630979005132954</v>
+      </c>
+      <c r="AK17">
+        <v>0.6406182574241889</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>First Financial Holding Co., Ltd. (TWSE:2892)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.0252</v>
+      </c>
+      <c r="E18">
+        <v>0.0571</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>763.3</v>
+      </c>
+      <c r="L18">
+        <v>0.3770313657693257</v>
+      </c>
+      <c r="M18">
+        <v>364.5</v>
+      </c>
+      <c r="N18">
+        <v>0.03142864533485087</v>
+      </c>
+      <c r="O18">
+        <v>0.4775317699462859</v>
+      </c>
+      <c r="P18">
+        <v>364.5</v>
+      </c>
+      <c r="Q18">
+        <v>0.03142864533485087</v>
+      </c>
+      <c r="R18">
+        <v>0.4775317699462859</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>1399.5</v>
+      </c>
+      <c r="V18">
+        <v>0.1206704777671435</v>
+      </c>
+      <c r="W18">
+        <v>0.1014959111761186</v>
+      </c>
+      <c r="X18">
+        <v>0.08941043126194514</v>
+      </c>
+      <c r="Y18">
+        <v>0.01208547991417346</v>
+      </c>
+      <c r="Z18">
+        <v>0.09608676048316286</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.06667567717719673</v>
+      </c>
+      <c r="AC18">
+        <v>-0.06667567717719673</v>
+      </c>
+      <c r="AD18">
+        <v>16808.9</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>16808.9</v>
+      </c>
+      <c r="AG18">
+        <v>15409.4</v>
+      </c>
+      <c r="AH18">
+        <v>0.5917251624622447</v>
+      </c>
+      <c r="AI18">
+        <v>0.6681466759415682</v>
+      </c>
+      <c r="AJ18">
+        <v>0.5705684801404075</v>
+      </c>
+      <c r="AK18">
+        <v>0.6485983668658979</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Taishin Financial Holding Co., Ltd. (TWSE:2887)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D12">
+      <c r="D19">
         <v>0.08400000000000001</v>
       </c>
-      <c r="E12">
+      <c r="E19">
         <v>0.07099999999999999</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
         <v>603.2</v>
       </c>
-      <c r="L12">
+      <c r="L19">
         <v>0.3281292498504053</v>
       </c>
-      <c r="M12">
+      <c r="M19">
         <v>235.7</v>
       </c>
-      <c r="N12">
+      <c r="N19">
         <v>0.03421992508493277</v>
       </c>
-      <c r="O12">
+      <c r="O19">
         <v>0.3907493368700265</v>
       </c>
-      <c r="P12">
+      <c r="P19">
         <v>235.7</v>
       </c>
-      <c r="Q12">
+      <c r="Q19">
         <v>0.03421992508493277</v>
       </c>
-      <c r="R12">
+      <c r="R19">
         <v>0.3907493368700265</v>
       </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
         <v>3227.4</v>
       </c>
-      <c r="V12">
+      <c r="V19">
         <v>0.4685676123000087</v>
       </c>
-      <c r="W12">
+      <c r="W19">
         <v>0.09773485855017985</v>
       </c>
-      <c r="X12">
-        <v>0.09536044013185979</v>
-      </c>
-      <c r="Y12">
-        <v>0.002374418418320062</v>
-      </c>
-      <c r="Z12">
+      <c r="X19">
+        <v>0.09533729491770462</v>
+      </c>
+      <c r="Y19">
+        <v>0.00239756363247523</v>
+      </c>
+      <c r="Z19">
         <v>0.1088266635093535</v>
       </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0.06674507299738625</v>
-      </c>
-      <c r="AC12">
-        <v>-0.06674507299738625</v>
-      </c>
-      <c r="AD12">
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.0667368543480867</v>
+      </c>
+      <c r="AC19">
+        <v>-0.0667368543480867</v>
+      </c>
+      <c r="AD19">
         <v>12509.5</v>
       </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
         <v>12509.5</v>
       </c>
-      <c r="AG12">
+      <c r="AG19">
         <v>9282.1</v>
       </c>
-      <c r="AH12">
+      <c r="AH19">
         <v>0.6449093430528992</v>
       </c>
-      <c r="AI12">
+      <c r="AI19">
         <v>0.6375502008032128</v>
       </c>
-      <c r="AJ12">
+      <c r="AJ19">
         <v>0.574035708322253</v>
       </c>
-      <c r="AK12">
+      <c r="AK19">
         <v>0.5661957569324989</v>
       </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
         <v>0</v>
       </c>
     </row>
